--- a/sendcleared-outreach-tracker.xlsx
+++ b/sendcleared-outreach-tracker.xlsx
@@ -1,29 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timothyarmstead/Sendcleared/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F286FE8-CFB2-3F45-92DB-92542E1BF411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8B207A-B42F-9746-893D-810316C03EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="1260" windowWidth="22400" windowHeight="16220" tabRatio="500" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3320" yWindow="600" windowWidth="27860" windowHeight="16220" tabRatio="500" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily Playbook" sheetId="1" r:id="rId1"/>
-    <sheet name="Lead Tracker" sheetId="2" r:id="rId2"/>
-    <sheet name="DM Templates" sheetId="3" r:id="rId3"/>
-    <sheet name="LinkedIn Requests" sheetId="4" r:id="rId4"/>
-    <sheet name="Weekly Scoreboard" sheetId="5" r:id="rId5"/>
-    <sheet name="Channel Strategy" sheetId="6" r:id="rId6"/>
-    <sheet name="Linked in Content Plan" sheetId="10" r:id="rId7"/>
-    <sheet name="Community Questions" sheetId="7" r:id="rId8"/>
-    <sheet name="Community Posts" sheetId="8" r:id="rId9"/>
-    <sheet name="Contacts " sheetId="9" r:id="rId10"/>
+    <sheet name="Overview" sheetId="12" r:id="rId1"/>
+    <sheet name="Daily Playbook" sheetId="1" r:id="rId2"/>
+    <sheet name="Lead Tracker" sheetId="2" r:id="rId3"/>
+    <sheet name="DM Templates" sheetId="3" r:id="rId4"/>
+    <sheet name="LinkedIn Requests" sheetId="4" r:id="rId5"/>
+    <sheet name="Weekly Scoreboard" sheetId="5" r:id="rId6"/>
+    <sheet name="Channel Strategy" sheetId="6" r:id="rId7"/>
+    <sheet name="Linked in Content Plan" sheetId="10" r:id="rId8"/>
+    <sheet name="Community Questions" sheetId="7" r:id="rId9"/>
+    <sheet name="SEO Content Plan" sheetId="11" r:id="rId10"/>
+    <sheet name="Community Posts" sheetId="8" r:id="rId11"/>
+    <sheet name="Contacts " sheetId="9" r:id="rId12"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId13"/>
+  </externalReferences>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="850">
   <si>
     <t>SendCleared — Daily Outreach Playbook  |  1 Hour / Day</t>
   </si>
@@ -1679,9 +1684,6 @@
     <t>https://www.linkedin.com/company/email-love/</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/company/badmarketing-digital/</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/company/digitalmarketingcompanyagency/</t>
   </si>
   <si>
@@ -1692,12 +1694,6 @@
   </si>
   <si>
     <t>https://www.linkedin.com/company/alpha-co-marketing-media/</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/company/less-is-moore-studios-email-marketing/</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/company/progressive-marketing2020/</t>
   </si>
   <si>
     <t>https://www.linkedin.com/company/marlomarketing/</t>
@@ -2116,15 +2112,565 @@
   <si>
     <t>Spencer Moore</t>
   </si>
+  <si>
+    <t>https://www.linkedin.com/in/saad-chaudhry-/</t>
+  </si>
+  <si>
+    <t>Saad Chaudhr</t>
+  </si>
+  <si>
+    <t>Progressive Marketing</t>
+  </si>
+  <si>
+    <t>Syed Manzar Hussain</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/manzar2000/</t>
+  </si>
+  <si>
+    <t>SEO Content Plan — 3 pillars, 3 cornerstones, 12 cluster posts</t>
+  </si>
+  <si>
+    <t>Each cornerstone is the pillar's cornerstone page; cluster posts link back to it. Ordered roughly TOFU → BOFU within each pillar.</t>
+  </si>
+  <si>
+    <t>Target keyword</t>
+  </si>
+  <si>
+    <t>Search intent</t>
+  </si>
+  <si>
+    <t>Funnel stage</t>
+  </si>
+  <si>
+    <t>Scheduled</t>
+  </si>
+  <si>
+    <t>Pillar 1 — QA / mistakes</t>
+  </si>
+  <si>
+    <t>Cornerstone</t>
+  </si>
+  <si>
+    <t>The Email QA Checklist for Agencies and Freelancers</t>
+  </si>
+  <si>
+    <t>email QA checklist</t>
+  </si>
+  <si>
+    <t>Informational</t>
+  </si>
+  <si>
+    <t>Week 2-3</t>
+  </si>
+  <si>
+    <t>Cluster</t>
+  </si>
+  <si>
+    <t>email personalization errors</t>
+  </si>
+  <si>
+    <t>TOFU</t>
+  </si>
+  <si>
+    <t>Week 7-8</t>
+  </si>
+  <si>
+    <t>Why your ESP can't catch these 5 mistakes</t>
+  </si>
+  <si>
+    <t>email QA vs ESP testing</t>
+  </si>
+  <si>
+    <t>Month 2</t>
+  </si>
+  <si>
+    <t>Not scheduled</t>
+  </si>
+  <si>
+    <t>pre-send email checklist</t>
+  </si>
+  <si>
+    <t>TOFU/MOFU</t>
+  </si>
+  <si>
+    <t>How to catch broken merge tags before sending</t>
+  </si>
+  <si>
+    <t>merge tag errors email</t>
+  </si>
+  <si>
+    <t>Informational, specific</t>
+  </si>
+  <si>
+    <t>MOFU</t>
+  </si>
+  <si>
+    <t>Pillar 2 — Approval / accountability</t>
+  </si>
+  <si>
+    <t>How to Get Client Sign-Off on Email Campaigns (Without the Slack Chaos)</t>
+  </si>
+  <si>
+    <t>client approval workflow email</t>
+  </si>
+  <si>
+    <t>Week 3-4</t>
+  </si>
+  <si>
+    <t>client email sign off checklist</t>
+  </si>
+  <si>
+    <t>Informational, shareable</t>
+  </si>
+  <si>
+    <t>Why "looks approved" isn't the same as "is approved"</t>
+  </si>
+  <si>
+    <t>The hidden cost of "just reply-all to approve"</t>
+  </si>
+  <si>
+    <t>email approval process for agencies</t>
+  </si>
+  <si>
+    <t>email approval audit trail</t>
+  </si>
+  <si>
+    <t>Commercial-adjacent</t>
+  </si>
+  <si>
+    <t>MOFU/BOFU</t>
+  </si>
+  <si>
+    <t>Month 3</t>
+  </si>
+  <si>
+    <t>Pillar 3 — Agency operations / trust</t>
+  </si>
+  <si>
+    <t>Running a Professional Email QA &amp; Approval Process as an Agency</t>
+  </si>
+  <si>
+    <t>email agency workflow</t>
+  </si>
+  <si>
+    <t>Week 5-6</t>
+  </si>
+  <si>
+    <t>email mistakes client trust</t>
+  </si>
+  <si>
+    <t>One approval hub for every ESP, not five logins</t>
+  </si>
+  <si>
+    <t>multi-ESP client approval</t>
+  </si>
+  <si>
+    <t>BOFU</t>
+  </si>
+  <si>
+    <t>From draft to approved: what a modern email workflow looks like</t>
+  </si>
+  <si>
+    <t>email approval software</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>How to Send a Test Email Your Client Can Actually Review</t>
+  </si>
+  <si>
+    <t>send test email (320/mo, difficulty 28)</t>
+  </si>
+  <si>
+    <t>Informational, high-intent</t>
+  </si>
+  <si>
+    <t>Why Emails Land in Spam: A Pre-Send Deliverability Checklist</t>
+  </si>
+  <si>
+    <t>how to stop emails going to spam (210/mo); spamhaus (1,600/mo)</t>
+  </si>
+  <si>
+    <t>The Anatomy of a Broken Email Link (and How to Catch It Before Sending)</t>
+  </si>
+  <si>
+    <t>html email link / link in html email (320/mo, difficulty 29-33)</t>
+  </si>
+  <si>
+    <t>NEW — Comparison Pages (zero competitor coverage found in keyword-gap analysis)</t>
+  </si>
+  <si>
+    <t>Comparison / competitive</t>
+  </si>
+  <si>
+    <t>Comparison</t>
+  </si>
+  <si>
+    <t>Litmus Alternative for Agencies and Freelancers</t>
+  </si>
+  <si>
+    <t>litmus alternative (no reported volume in gap data — untapped)</t>
+  </si>
+  <si>
+    <t>Commercial, high-intent</t>
+  </si>
+  <si>
+    <t>Email on Acid vs SendCleared: Which One Do You Actually Need?</t>
+  </si>
+  <si>
+    <t>email on acid alternative (no reported volume — untapped)</t>
+  </si>
+  <si>
+    <t>Commercial, comparison</t>
+  </si>
+  <si>
+    <t>Why Generic Proofing Tools (Ziflow, Filestage, Ashore) Don't Work for Email</t>
+  </si>
+  <si>
+    <t>email approval software (no direct competitor overlap found)</t>
+  </si>
+  <si>
+    <t>The Best Client Approval Tool for Email Marketers (2026)</t>
+  </si>
+  <si>
+    <t>email approval software / client sign off tool</t>
+  </si>
+  <si>
+    <t>Rows 1-4 (orange) are scheduled into the Daily Plan tab, weeks 1-8. Rows 5-18 are Month 2-3 backlog. Rows 19-22 (blue) are new comparison pages, added from the Litmus/Mailtrap/Email on Acid keyword-gap analysis — none of the three competitors rank for approval, sign-off, proofing, or freelance terms, and no 'alternative'/'vs' comparison content exists yet for this category.</t>
+  </si>
+  <si>
+    <t>SendCleared — Customer Growth Plan</t>
+  </si>
+  <si>
+    <t>2 hrs/day · 8-week build-out · Freelancer + Agency acquisition</t>
+  </si>
+  <si>
+    <t>Plan start date</t>
+  </si>
+  <si>
+    <t>Plan length</t>
+  </si>
+  <si>
+    <t>8 weeks (40 working days)</t>
+  </si>
+  <si>
+    <t>Daily time budget</t>
+  </si>
+  <si>
+    <t>120 minutes</t>
+  </si>
+  <si>
+    <t>Phase plan</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Weeks</t>
+  </si>
+  <si>
+    <t>Primary goal</t>
+  </si>
+  <si>
+    <t>Phase 1</t>
+  </si>
+  <si>
+    <t>Weeks 1-2</t>
+  </si>
+  <si>
+    <t>Foundation: approval-led LP, beta agency recruiting, analytics setup</t>
+  </si>
+  <si>
+    <t>10 beta agencies onboarded, tracking live</t>
+  </si>
+  <si>
+    <t>Phase 2</t>
+  </si>
+  <si>
+    <t>Weeks 3-4</t>
+  </si>
+  <si>
+    <t>Community presence, SEO content, first case studies</t>
+  </si>
+  <si>
+    <t>3 SEO posts live, 2 testimonials, organic signups begin</t>
+  </si>
+  <si>
+    <t>Phase 3</t>
+  </si>
+  <si>
+    <t>Weeks 5-6</t>
+  </si>
+  <si>
+    <t>Public pricing launch, directory listings, Product Hunt</t>
+  </si>
+  <si>
+    <t>Stripe live, first paying customers</t>
+  </si>
+  <si>
+    <t>Phase 4</t>
+  </si>
+  <si>
+    <t>Weeks 7-8</t>
+  </si>
+  <si>
+    <t>Scale content + outreach, partnerships, retro</t>
+  </si>
+  <si>
+    <t>Compounding organic traffic, plan next 8 weeks</t>
+  </si>
+  <si>
+    <t>Weekly rhythm (Mon-Fri)</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Monday</t>
+  </si>
+  <si>
+    <t>SEO / Content</t>
+  </si>
+  <si>
+    <t>Keyword research, drafting, publishing, on-page optimisation</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>Cold email</t>
+  </si>
+  <si>
+    <t>Building target lists, outreach batches, follow-ups</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>Community / answering questions</t>
+  </si>
+  <si>
+    <t>Reddit, Slack/Discord, Indie Hackers, X — genuine engagement, no pitching</t>
+  </si>
+  <si>
+    <t>Thursday</t>
+  </si>
+  <si>
+    <t>Listings / partnerships</t>
+  </si>
+  <si>
+    <t>Directories, partner programmes, Product Hunt, affiliate/cross-promo</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>Metrics + admin</t>
+  </si>
+  <si>
+    <t>Weekly review, testimonials, case studies, pricing/ops tasks</t>
+  </si>
+  <si>
+    <t>Progress summary (auto-updates from Daily Plan tab)</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Total tasks</t>
+  </si>
+  <si>
+    <t>Tasks done</t>
+  </si>
+  <si>
+    <t>Tasks in progress</t>
+  </si>
+  <si>
+    <t>Tasks not started</t>
+  </si>
+  <si>
+    <t>% complete</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kevin-parady/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/lucyovers/</t>
+  </si>
+  <si>
+    <t>Lucy Overs</t>
+  </si>
+  <si>
+    <t>Kevin Parady</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/belyndamurray/</t>
+  </si>
+  <si>
+    <t>Belynda (Belle) Murray</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/plamen-tonev/</t>
+  </si>
+  <si>
+    <t>Plamen Tonev</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tizian-bauer/</t>
+  </si>
+  <si>
+    <t>Tizian Bauer</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/anwesha-singh-6996ab153/</t>
+  </si>
+  <si>
+    <t>Anwesha Singh</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jeremyklaviyo/</t>
+  </si>
+  <si>
+    <t>Jeremy Vincent R. Dela Cruz</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jocelyn-abel-85a903149/</t>
+  </si>
+  <si>
+    <t>Jocelyn Abel</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/rakic-milos/</t>
+  </si>
+  <si>
+    <t>Milos Rakic</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/letitia-tita-b45712100/</t>
+  </si>
+  <si>
+    <t>Letitia Tita</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/alen-capelja/</t>
+  </si>
+  <si>
+    <t>Alen Capelja</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/christina-vasiliadou/</t>
+  </si>
+  <si>
+    <t>Christina Vasiliadou</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/david-jim/</t>
+  </si>
+  <si>
+    <t>David Jimenez</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/andreea-maria-micl%C4%83u%C8%99-8b1474b8/</t>
+  </si>
+  <si>
+    <t>Andreea-Maria Miclaus</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/lauraserbest/</t>
+  </si>
+  <si>
+    <t>Laura S.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/peyman-karimian/</t>
+  </si>
+  <si>
+    <t>Peyman Karimian</t>
+  </si>
+  <si>
+    <t>Biljana Dukleska</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/biljana-dukleska-a1b48132/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/idris-farjad-622846197/</t>
+  </si>
+  <si>
+    <t>Idris Farjad</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/robson-esteves/?locale=en</t>
+  </si>
+  <si>
+    <t>Robson Esteves Daniel</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/areeba-ahmed-1535b6180/</t>
+  </si>
+  <si>
+    <t>Areeba Ahmed</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/laura-vaakanainen/</t>
+  </si>
+  <si>
+    <t>Laura Vaakanainen</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/emilythrockmorton/</t>
+  </si>
+  <si>
+    <t>Emily Throckmorton</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/danielghiroltean/</t>
+  </si>
+  <si>
+    <t>Daniel Ghiroltean</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/markokoprivica/</t>
+  </si>
+  <si>
+    <t>Marko Koprivica</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sumant-goyal-3b957030b/</t>
+  </si>
+  <si>
+    <t>Sumant Goyal</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tierraexum/</t>
+  </si>
+  <si>
+    <t>Tierra Grosman</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/leon-matthew-989354206/</t>
+  </si>
+  <si>
+    <t>Leon Matthew</t>
+  </si>
+  <si>
+    <t>15.09.26</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yy"/>
+    <numFmt numFmtId="165" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2239,8 +2785,28 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF134E8E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF134E8E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2283,6 +2849,18 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDECE3"/>
+        <bgColor rgb="FFF7F7F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F0F8"/>
+        <bgColor rgb="FFF7F7F5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2311,7 +2889,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2355,11 +2933,34 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2368,11 +2969,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2456,6 +3058,788 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="Daily Plan"/>
+      <sheetName val="Task Library"/>
+      <sheetName val="SEO Content Plan"/>
+      <sheetName val="Metrics Tracker"/>
+      <sheetName val="LinkedIn Content Plan"/>
+      <sheetName val="Outreach Emails"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="F2" t="str">
+            <v>Keyword research: list 15 target long-tail queries (e.g. "email QA checklist", "client approval workflow for email campaigns")</v>
+          </cell>
+          <cell r="H2" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="F3" t="str">
+            <v>Audit current LP copy against approval-first positioning; note gaps</v>
+          </cell>
+          <cell r="H3" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="F4" t="str">
+            <v>Write &amp; publish LinkedIn article #1: "The £47 email mistake no one talks about" (QA / mistakes)</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5" t="str">
+            <v>Build target list of 30 agencies from Klaviyo/Mailchimp partner directories (name, contact, ESP)</v>
+          </cell>
+          <cell r="H5" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6" t="str">
+            <v>Draft cold email template v1 for beta invite</v>
+          </cell>
+          <cell r="H6" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="F7" t="str">
+            <v>Join r/emailmarketing, r/freelance, r/agency + 2 relevant Slack/Discord communities</v>
+          </cell>
+          <cell r="H7" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="F8" t="str">
+            <v>Introduce yourself in each — no pitching, just context</v>
+          </cell>
+          <cell r="H8" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="F9" t="str">
+            <v>Bookmark 5 recent threads relevant to email QA/approval to answer next week</v>
+          </cell>
+          <cell r="H9" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="F10" t="str">
+            <v>Research and shortlist 8 "best tools for agencies" directories to submit to</v>
+          </cell>
+          <cell r="H10" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="F11" t="str">
+            <v>Submit to first 3 directories</v>
+          </cell>
+          <cell r="H11" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="F12" t="str">
+            <v>Set up growth tracker: approval links sent, free signups, paid signups, MRR (this workbook)</v>
+          </cell>
+          <cell r="H12" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="F13" t="str">
+            <v>Weekly review: log baseline numbers, note blockers for week 2</v>
+          </cell>
+          <cell r="H13" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="F14" t="str">
+            <v>Draft Cornerstone 1: "The Email QA Checklist for Agencies and Freelancers" (Pillar 1 cornerstone page)</v>
+          </cell>
+          <cell r="H14" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="F15" t="str">
+            <v>Write &amp; publish LinkedIn article #2: "Why 'looks approved' isn't the same as 'is approved'" (Approval / accountability)</v>
+          </cell>
+          <cell r="H15" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="F16" t="str">
+            <v>Send cold email batch 1 — 10 agencies, beta invite (free access + feedback call)</v>
+          </cell>
+          <cell r="H16" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="F17" t="str">
+            <v>Log responses / set follow-up reminders</v>
+          </cell>
+          <cell r="H17" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="F18" t="str">
+            <v>Answer 3 genuine questions across communities joined last week (no pitch)</v>
+          </cell>
+          <cell r="H18" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="F19" t="str">
+            <v>Share one useful resource/checklist where relevant</v>
+          </cell>
+          <cell r="H19" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="F20" t="str">
+            <v>Note any recurring pain points people mention</v>
+          </cell>
+          <cell r="H20" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="F21" t="str">
+            <v>Submit to 3 more directories</v>
+          </cell>
+          <cell r="H21" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="F22" t="str">
+            <v>Start Product Hunt prep: draft tagline, gallery assets list, launch date target</v>
+          </cell>
+          <cell r="H22" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="F23" t="str">
+            <v>Weekly review: update tracker</v>
+          </cell>
+          <cell r="H23" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="F24" t="str">
+            <v>Ask 2 active beta agencies for a short testimonial</v>
+          </cell>
+          <cell r="H24" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="F25" t="str">
+            <v>Plan week 3 priorities based on beta feedback</v>
+          </cell>
+          <cell r="H25" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="F26" t="str">
+            <v>Edit + publish Cornerstone 1; submit URL to Google Search Console</v>
+          </cell>
+          <cell r="H26" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="F27" t="str">
+            <v>Add 2 internal links from LP/report page to the post</v>
+          </cell>
+          <cell r="H27" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="F28" t="str">
+            <v>Draft outline for Cornerstone 2: "How to Get Client Sign-Off on Email Campaigns (Without the Slack Chaos)" (Pillar 2 cornerstone page)</v>
+          </cell>
+          <cell r="H28" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="F29" t="str">
+            <v>Write &amp; publish LinkedIn article #3: "The 3 questions every client should ask before hitting send" (Approval / accountability)</v>
+          </cell>
+          <cell r="H29" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="F30" t="str">
+            <v>Write &amp; publish LinkedIn article #4: "What I learned reviewing 500 client emails before they went out" (QA / mistakes)</v>
+          </cell>
+          <cell r="H30" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="F31" t="str">
+            <v>Follow up batch 1 non-responders (personalised, reference their ESP/clients)</v>
+          </cell>
+          <cell r="H31" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="F32" t="str">
+            <v>Send cold email batch 2 — 10 more agencies</v>
+          </cell>
+          <cell r="H32" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="F33" t="str">
+            <v>Answer 3 more questions across communities</v>
+          </cell>
+          <cell r="H33" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="F34" t="str">
+            <v>Post an "ask me anything about email QA" style thread in one community</v>
+          </cell>
+          <cell r="H34" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="F35" t="str">
+            <v>Submit to Klaviyo/Mailchimp partner or agency directories specifically</v>
+          </cell>
+          <cell r="H35" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="F36" t="str">
+            <v>Reach out to 3 complementary tool makers (ESP consultants, freelance platforms) re: cross-promo</v>
+          </cell>
+          <cell r="H36" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="F37" t="str">
+            <v>Weekly review: update tracker</v>
+          </cell>
+          <cell r="H37" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="F38" t="str">
+            <v>Draft case study #1 from best-performing beta agency</v>
+          </cell>
+          <cell r="H38" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="F39" t="str">
+            <v>Write and publish Cornerstone 2 (client sign-off / audit trail cornerstone)</v>
+          </cell>
+          <cell r="H39" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="F40" t="str">
+            <v>Write &amp; publish LinkedIn article #5: "The hidden cost of 'just reply-all to approve'" (Approval / accountability)</v>
+          </cell>
+          <cell r="H40" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="F41" t="str">
+            <v>Follow up batch 2 non-responders</v>
+          </cell>
+          <cell r="H41" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="F42" t="str">
+            <v>Send cold email batch 3 — 10 freelancers via Upwork/LinkedIn search</v>
+          </cell>
+          <cell r="H42" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="F43" t="str">
+            <v>First Indie Hackers "build in public" post — share journey, early numbers</v>
+          </cell>
+          <cell r="H43" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="F44" t="str">
+            <v>Respond to any comments/DMs from the post</v>
+          </cell>
+          <cell r="H44" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="F45" t="str">
+            <v>Follow up on directory listings — confirm live, fix broken ones</v>
+          </cell>
+          <cell r="H45" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="F46" t="str">
+            <v>Continue partnership outreach follow-ups</v>
+          </cell>
+          <cell r="H46" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="F47" t="str">
+            <v>Finalise Product Hunt assets and copy</v>
+          </cell>
+          <cell r="H47" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="F48" t="str">
+            <v>Weekly review: update tracker</v>
+          </cell>
+          <cell r="H48" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="F49" t="str">
+            <v>Publish case study #1 on LP / as a post</v>
+          </cell>
+          <cell r="H49" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="F50" t="str">
+            <v>Draft outline + write Cornerstone 3: "Running a Professional Email QA &amp; Approval Process as an Agency" (Pillar 3 cornerstone page)</v>
+          </cell>
+          <cell r="H50" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="F51" t="str">
+            <v>Write &amp; publish LinkedIn article #6: "How agencies lose client trust in one broken subject line" (Agency operations / trust)</v>
+          </cell>
+          <cell r="H51" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="F52" t="str">
+            <v>Send cold email batch 4 — 10 agencies, include pricing launch + case study</v>
+          </cell>
+          <cell r="H52" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="F53" t="str">
+            <v>Log + follow-up reminders</v>
+          </cell>
+          <cell r="H53" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="F54" t="str">
+            <v>Answer 3 questions + soft-mention case study result where genuinely relevant</v>
+          </cell>
+          <cell r="H54" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="F55" t="str">
+            <v>Engage on X/Twitter: 2 threads about email QA/approval pain points</v>
+          </cell>
+          <cell r="H55" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="F56" t="str">
+            <v>Stripe pricing go-live checklist: plans, webhooks, upgrade prompts — QA test end to end</v>
+          </cell>
+          <cell r="H56" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="F57" t="str">
+            <v>Update all directory listings with live pricing</v>
+          </cell>
+          <cell r="H57" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="F58" t="str">
+            <v>Weekly review: update tracker</v>
+          </cell>
+          <cell r="H58" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="F59" t="str">
+            <v>Confirm Stripe live in production; test one real checkout</v>
+          </cell>
+          <cell r="H59" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="F60" t="str">
+            <v>Announce pricing launch to beta agencies + email list</v>
+          </cell>
+          <cell r="H60" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="F61" t="str">
+            <v>Publish Cornerstone 3 + submit to Search Console</v>
+          </cell>
+          <cell r="H61" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="F62" t="str">
+            <v>Review Search Console data from posts 1-2, fix any indexing issues</v>
+          </cell>
+          <cell r="H62" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="F63" t="str">
+            <v>Write &amp; publish LinkedIn article #7: "The pre-send checklist top email agencies actually use" (QA / mistakes)</v>
+          </cell>
+          <cell r="H63" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="F64" t="str">
+            <v>Write &amp; publish LinkedIn article #8: "Why your ESP can't catch these 5 mistakes (but your process should)" (QA / mistakes)</v>
+          </cell>
+          <cell r="H64" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="F65" t="str">
+            <v>Personalised outreach to 10 warm leads from free-tier signups (usage-based)</v>
+          </cell>
+          <cell r="H65" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="F66" t="str">
+            <v>Log + follow-up reminders</v>
+          </cell>
+          <cell r="H66" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="F67" t="str">
+            <v>Indie Hackers post #2 — share case study results / early revenue</v>
+          </cell>
+          <cell r="H67" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="F68" t="str">
+            <v>Respond to comments/DMs</v>
+          </cell>
+          <cell r="H68" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="F69" t="str">
+            <v>Product Hunt launch day: post, respond to every comment, share in communities</v>
+          </cell>
+          <cell r="H69" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="F70" t="str">
+            <v>Weekly review: update tracker incl. Product Hunt referral traffic</v>
+          </cell>
+          <cell r="H70" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="F71" t="str">
+            <v>Follow up Product Hunt leads individually</v>
+          </cell>
+          <cell r="H71" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="F72" t="str">
+            <v>Gather 2 more testimonials from newly paying customers</v>
+          </cell>
+          <cell r="H72" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="F73" t="str">
+            <v>Review SEO Content Plan tab; confirm next 3 cluster posts for weeks 9+ based on Search Console queries so far</v>
+          </cell>
+          <cell r="H73" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="F74" t="str">
+            <v>Draft cluster post: "The £47 email mistake no one talks about" (Pillar 1, TOFU, links back to Cornerstone 1)</v>
+          </cell>
+          <cell r="H74" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="F75" t="str">
+            <v>Write &amp; publish LinkedIn article #9: "The audit trail your client is quietly expecting" (Approval / accountability)</v>
+          </cell>
+          <cell r="H75" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="F76" t="str">
+            <v>Send cold email batch 5 — 15 agencies, attach case study PDF</v>
+          </cell>
+          <cell r="H76" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="F77" t="str">
+            <v>Log + follow-up reminders</v>
+          </cell>
+          <cell r="H77" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="F78" t="str">
+            <v>Answer 3 questions across communities</v>
+          </cell>
+          <cell r="H78" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="F79" t="str">
+            <v>Engage on X/Twitter: 2 threads</v>
+          </cell>
+          <cell r="H79" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="F80" t="str">
+            <v>Partnership outreach follow-ups — aim to confirm 1-2 cross-promotions</v>
+          </cell>
+          <cell r="H80" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="F81" t="str">
+            <v>Explore + scope a simple affiliate/referral program</v>
+          </cell>
+          <cell r="H81" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="F82" t="str">
+            <v>Weekly review: update tracker</v>
+          </cell>
+          <cell r="H82" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="F83" t="str">
+            <v>Publish blog post 4</v>
+          </cell>
+          <cell r="H83" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="F84" t="str">
+            <v>Draft case study #2</v>
+          </cell>
+          <cell r="H84" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="F85" t="str">
+            <v>Publish + promote cluster post: "The £47 email mistake no one talks about" (share in communities, X)</v>
+          </cell>
+          <cell r="H85" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="F86" t="str">
+            <v>Refresh meta titles/descriptions on posts 1-3 based on performance</v>
+          </cell>
+          <cell r="H86" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="F87" t="str">
+            <v>Write &amp; publish LinkedIn article #10: "From draft to approved: what a modern email workflow actually looks like" (Agency operations / trust)</v>
+          </cell>
+          <cell r="H87" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="F88" t="str">
+            <v>Re-engage full cold list with a short nurture email (what's new, case studies, pricing)</v>
+          </cell>
+          <cell r="H88" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="89">
+          <cell r="F89" t="str">
+            <v>Log responses</v>
+          </cell>
+          <cell r="H89" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="90">
+          <cell r="F90" t="str">
+            <v>Review engagement across all communities — identify top 3 by response/signups</v>
+          </cell>
+          <cell r="H90" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="91">
+          <cell r="F91" t="str">
+            <v>Double down: post/answer in the top 3 only going forward</v>
+          </cell>
+          <cell r="H91" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="F92" t="str">
+            <v>Review directory referral traffic — keep top performers, drop dead listings</v>
+          </cell>
+          <cell r="H92" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="93">
+          <cell r="F93" t="str">
+            <v>Confirm any partnerships/affiliate agreements in writing</v>
+          </cell>
+          <cell r="H93" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="94">
+          <cell r="F94" t="str">
+            <v>Full 8-week retro: what worked, what to cut, MRR vs target</v>
+          </cell>
+          <cell r="H94" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+        <row r="95">
+          <cell r="F95" t="str">
+            <v>Plan next 8-week growth cycle using this tracker as a template</v>
+          </cell>
+          <cell r="H95" t="str">
+            <v>Not started</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2636,6 +4020,3707 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B93E062D-B4D5-E649-922C-35A0023B2BDB}">
+  <dimension ref="A1:F31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="23" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="34" t="s">
+        <v>744</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="14" t="s">
+        <v>745</v>
+      </c>
+      <c r="B4" s="27">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="14" t="s">
+        <v>746</v>
+      </c>
+      <c r="B5" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="14" t="s">
+        <v>748</v>
+      </c>
+      <c r="B6" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="28" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
+        <v>751</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>752</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="17" t="s">
+        <v>758</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>759</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>760</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="17" t="s">
+        <v>766</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>767</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>768</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="28" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>771</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="17" t="s">
+        <v>776</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>777</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A21" s="17" t="s">
+        <v>782</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>783</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="28" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="6" t="s">
+        <v>790</v>
+      </c>
+      <c r="B27" s="6">
+        <f>COUNTA('[1]Daily Plan'!F2:F200)</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="B28" s="16" t="e">
+        <f>COUNTIF('[1]Daily Plan'!H2:H200,"Done")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>792</v>
+      </c>
+      <c r="B29" s="6" t="e">
+        <f>COUNTIF('[1]Daily Plan'!H2:H200,"In progress")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="16" t="s">
+        <v>793</v>
+      </c>
+      <c r="B30" s="16" t="e">
+        <f>COUNTIF('[1]Daily Plan'!H2:H200,"Not started")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="6" t="s">
+        <v>794</v>
+      </c>
+      <c r="B31" s="29">
+        <f>IFERROR(B28/B27,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A1B1F60-9988-B74B-B926-965FAE72EE02}">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="40" t="s">
+        <v>672</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+    </row>
+    <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+    </row>
+    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>674</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>675</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>676</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="21">
+        <v>1</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>680</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>681</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>682</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>683</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="23">
+        <v>2</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>678</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>685</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>682</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>686</v>
+      </c>
+      <c r="H6" s="23" t="s">
+        <v>687</v>
+      </c>
+      <c r="I6" s="23" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="24">
+        <v>3</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>678</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>684</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>682</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>686</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>690</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="23">
+        <v>4</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>678</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>692</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>682</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>693</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>690</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A9" s="24">
+        <v>5</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>678</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>684</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>696</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>697</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>690</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="21">
+        <v>6</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>698</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>699</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>700</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>682</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>701</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="24">
+        <v>7</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>698</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>684</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>703</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>686</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>690</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="23">
+        <v>8</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>698</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>704</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>700</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>682</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>697</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>690</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="24">
+        <v>9</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>698</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>684</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>682</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>697</v>
+      </c>
+      <c r="H13" s="24" t="s">
+        <v>690</v>
+      </c>
+      <c r="I13" s="24" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="23">
+        <v>10</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>698</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>707</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>708</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>709</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>710</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="21">
+        <v>11</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>711</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>712</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>713</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>682</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>679</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>714</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A16" s="23">
+        <v>12</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>711</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>715</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>682</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>686</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>690</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A17" s="24">
+        <v>13</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>711</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>684</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>682</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>697</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>690</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="23">
+        <v>14</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>711</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>716</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>708</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>718</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>710</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A19" s="24">
+        <v>15</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>711</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>684</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="F19" s="24" t="s">
+        <v>721</v>
+      </c>
+      <c r="G19" s="24" t="s">
+        <v>718</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>710</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A20" s="17">
+        <v>16</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>678</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>722</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>723</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>724</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>693</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>691</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="A21" s="25">
+        <v>17</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>678</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>725</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>726</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>682</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>686</v>
+      </c>
+      <c r="H21" s="17" t="s">
+        <v>691</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A22" s="17">
+        <v>18</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>678</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>684</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>727</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>728</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>696</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>697</v>
+      </c>
+      <c r="H22" s="17" t="s">
+        <v>691</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="30" t="s">
+        <v>729</v>
+      </c>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+    </row>
+    <row r="25" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A25" s="26">
+        <v>19</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>730</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>731</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>732</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>733</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>734</v>
+      </c>
+      <c r="G25" s="26" t="s">
+        <v>718</v>
+      </c>
+      <c r="H25" s="26" t="s">
+        <v>691</v>
+      </c>
+      <c r="I25" s="26" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A26" s="26">
+        <v>20</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>730</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>731</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>735</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>736</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>737</v>
+      </c>
+      <c r="G26" s="26" t="s">
+        <v>718</v>
+      </c>
+      <c r="H26" s="26" t="s">
+        <v>691</v>
+      </c>
+      <c r="I26" s="26" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="A27" s="26">
+        <v>21</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>730</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>731</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>738</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>739</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>737</v>
+      </c>
+      <c r="G27" s="26" t="s">
+        <v>718</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>691</v>
+      </c>
+      <c r="I27" s="26" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A28" s="26">
+        <v>22</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>730</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>731</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>740</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>741</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>721</v>
+      </c>
+      <c r="G28" s="26" t="s">
+        <v>718</v>
+      </c>
+      <c r="H28" s="26" t="s">
+        <v>691</v>
+      </c>
+      <c r="I28" s="26" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="42" t="s">
+        <v>742</v>
+      </c>
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A30:I30"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="I5:I28" xr:uid="{4F8A411F-8E1F-3441-9559-F765E05CA472}">
+      <formula1>"Not started,Not scheduled,Drafted,Published"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C59208D-E153-D94F-949B-1D2F26D7FF23}">
+  <dimension ref="A1:I202"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>551</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B4" t="s">
+        <v>416</v>
+      </c>
+      <c r="D4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E5" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>464</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" t="s">
+        <v>467</v>
+      </c>
+      <c r="E6" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D7" t="s">
+        <v>417</v>
+      </c>
+      <c r="E7" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>333</v>
+      </c>
+      <c r="B8" t="s">
+        <v>416</v>
+      </c>
+      <c r="D8" t="s">
+        <v>412</v>
+      </c>
+      <c r="E8" t="s">
+        <v>554</v>
+      </c>
+      <c r="H8" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>349</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E9" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>347</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>470</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" t="s">
+        <v>471</v>
+      </c>
+      <c r="F11" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>458</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" t="s">
+        <v>459</v>
+      </c>
+      <c r="F12" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>320</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" t="s">
+        <v>457</v>
+      </c>
+      <c r="E13" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>341</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" t="s">
+        <v>423</v>
+      </c>
+      <c r="E14" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" t="s">
+        <v>427</v>
+      </c>
+      <c r="H15" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>330</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" t="s">
+        <v>496</v>
+      </c>
+      <c r="E16" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>324</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" t="s">
+        <v>495</v>
+      </c>
+      <c r="E17" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>455</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" t="s">
+        <v>456</v>
+      </c>
+      <c r="F18" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>300</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" t="s">
+        <v>490</v>
+      </c>
+      <c r="E19" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>332</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" t="s">
+        <v>494</v>
+      </c>
+      <c r="E20" t="s">
+        <v>554</v>
+      </c>
+      <c r="I20" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>303</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" t="s">
+        <v>493</v>
+      </c>
+      <c r="E21" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>446</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" t="s">
+        <v>445</v>
+      </c>
+      <c r="E22" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>328</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" t="s">
+        <v>433</v>
+      </c>
+      <c r="E23" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>350</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" t="s">
+        <v>440</v>
+      </c>
+      <c r="E24" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>474</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" t="s">
+        <v>475</v>
+      </c>
+      <c r="E25" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>348</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>447</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" t="s">
+        <v>448</v>
+      </c>
+      <c r="E27" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>468</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" t="s">
+        <v>469</v>
+      </c>
+      <c r="E28" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>343</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" t="s">
+        <v>425</v>
+      </c>
+      <c r="E29" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>472</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" t="s">
+        <v>473</v>
+      </c>
+      <c r="E30" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>478</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" t="s">
+        <v>477</v>
+      </c>
+      <c r="E31" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>323</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" t="s">
+        <v>432</v>
+      </c>
+      <c r="E32" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>317</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" t="s">
+        <v>489</v>
+      </c>
+      <c r="E33" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>465</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" t="s">
+        <v>466</v>
+      </c>
+      <c r="E34" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>308</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C35" s="19"/>
+      <c r="D35" t="s">
+        <v>431</v>
+      </c>
+      <c r="G35" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>331</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" t="s">
+        <v>434</v>
+      </c>
+      <c r="E36" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>298</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" t="s">
+        <v>486</v>
+      </c>
+      <c r="E37" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>312</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" t="s">
+        <v>485</v>
+      </c>
+      <c r="E38" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>299</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" t="s">
+        <v>484</v>
+      </c>
+      <c r="E39" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>314</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" t="s">
+        <v>483</v>
+      </c>
+      <c r="E40" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>449</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" t="s">
+        <v>450</v>
+      </c>
+      <c r="E41" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>334</v>
+      </c>
+      <c r="B42" t="s">
+        <v>416</v>
+      </c>
+      <c r="D42" t="s">
+        <v>413</v>
+      </c>
+      <c r="E42" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>443</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C43" s="19"/>
+      <c r="D43" t="s">
+        <v>444</v>
+      </c>
+      <c r="E43" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>442</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C44" s="19"/>
+      <c r="D44" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>451</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C45" s="19"/>
+      <c r="D45" t="s">
+        <v>452</v>
+      </c>
+      <c r="E45" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>318</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C46" s="19"/>
+      <c r="D46" t="s">
+        <v>482</v>
+      </c>
+      <c r="E46" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>326</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C47" s="19"/>
+      <c r="D47" t="s">
+        <v>481</v>
+      </c>
+      <c r="E47" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>329</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C48" s="19"/>
+      <c r="D48" t="s">
+        <v>480</v>
+      </c>
+      <c r="E48" t="s">
+        <v>555</v>
+      </c>
+      <c r="F48" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>462</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C49" s="19"/>
+      <c r="D49" t="s">
+        <v>463</v>
+      </c>
+      <c r="E49" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>302</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C50" s="19"/>
+      <c r="D50" t="s">
+        <v>428</v>
+      </c>
+      <c r="E50" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>325</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C51" s="19"/>
+      <c r="D51" t="s">
+        <v>479</v>
+      </c>
+      <c r="E51" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>307</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C52" s="19"/>
+      <c r="D52" t="s">
+        <v>430</v>
+      </c>
+      <c r="E52" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>316</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C53" s="19"/>
+      <c r="D53" t="s">
+        <v>499</v>
+      </c>
+      <c r="E53" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>319</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C54" s="19"/>
+      <c r="D54" t="s">
+        <v>501</v>
+      </c>
+      <c r="E54" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>321</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C55" s="19"/>
+      <c r="D55" t="s">
+        <v>502</v>
+      </c>
+      <c r="E55" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>305</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C56" s="19"/>
+      <c r="D56" t="s">
+        <v>503</v>
+      </c>
+      <c r="E56" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>304</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C57" s="19"/>
+      <c r="D57" t="s">
+        <v>504</v>
+      </c>
+      <c r="E57" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>517</v>
+      </c>
+      <c r="B58" t="s">
+        <v>416</v>
+      </c>
+      <c r="D58" t="s">
+        <v>518</v>
+      </c>
+      <c r="E58" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>519</v>
+      </c>
+      <c r="B59" t="s">
+        <v>416</v>
+      </c>
+      <c r="D59" t="s">
+        <v>520</v>
+      </c>
+      <c r="E59" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>521</v>
+      </c>
+      <c r="B60" t="s">
+        <v>416</v>
+      </c>
+      <c r="D60" t="s">
+        <v>522</v>
+      </c>
+      <c r="E60" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>523</v>
+      </c>
+      <c r="B61" t="s">
+        <v>416</v>
+      </c>
+      <c r="D61" t="s">
+        <v>524</v>
+      </c>
+      <c r="E61" t="s">
+        <v>555</v>
+      </c>
+      <c r="H61" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>507</v>
+      </c>
+      <c r="B62" t="s">
+        <v>416</v>
+      </c>
+      <c r="D62" t="s">
+        <v>508</v>
+      </c>
+      <c r="E62" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>511</v>
+      </c>
+      <c r="B63" t="s">
+        <v>416</v>
+      </c>
+      <c r="D63" t="s">
+        <v>512</v>
+      </c>
+      <c r="E63" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>513</v>
+      </c>
+      <c r="B64" t="s">
+        <v>416</v>
+      </c>
+      <c r="D64" t="s">
+        <v>514</v>
+      </c>
+      <c r="E64" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>516</v>
+      </c>
+      <c r="B65" t="s">
+        <v>416</v>
+      </c>
+      <c r="D65" t="s">
+        <v>515</v>
+      </c>
+      <c r="E65" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>795</v>
+      </c>
+      <c r="B66" t="s">
+        <v>416</v>
+      </c>
+      <c r="D66" t="s">
+        <v>798</v>
+      </c>
+      <c r="E66" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>796</v>
+      </c>
+      <c r="B67" t="s">
+        <v>416</v>
+      </c>
+      <c r="D67" t="s">
+        <v>797</v>
+      </c>
+      <c r="E67" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>799</v>
+      </c>
+      <c r="B68" t="s">
+        <v>416</v>
+      </c>
+      <c r="D68" t="s">
+        <v>800</v>
+      </c>
+      <c r="E68" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>801</v>
+      </c>
+      <c r="B69" t="s">
+        <v>416</v>
+      </c>
+      <c r="D69" t="s">
+        <v>802</v>
+      </c>
+      <c r="E69" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>803</v>
+      </c>
+      <c r="B70" t="s">
+        <v>416</v>
+      </c>
+      <c r="D70" t="s">
+        <v>804</v>
+      </c>
+      <c r="E70" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>805</v>
+      </c>
+      <c r="B71" t="s">
+        <v>416</v>
+      </c>
+      <c r="D71" t="s">
+        <v>806</v>
+      </c>
+      <c r="E71" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>807</v>
+      </c>
+      <c r="B72" t="s">
+        <v>416</v>
+      </c>
+      <c r="D72" t="s">
+        <v>808</v>
+      </c>
+      <c r="E72" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>809</v>
+      </c>
+      <c r="B73" t="s">
+        <v>416</v>
+      </c>
+      <c r="D73" t="s">
+        <v>810</v>
+      </c>
+      <c r="E73" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>811</v>
+      </c>
+      <c r="B74" t="s">
+        <v>416</v>
+      </c>
+      <c r="D74" t="s">
+        <v>812</v>
+      </c>
+      <c r="E74" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>813</v>
+      </c>
+      <c r="B75" t="s">
+        <v>416</v>
+      </c>
+      <c r="D75" t="s">
+        <v>814</v>
+      </c>
+      <c r="E75" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>815</v>
+      </c>
+      <c r="B76" t="s">
+        <v>416</v>
+      </c>
+      <c r="D76" t="s">
+        <v>816</v>
+      </c>
+      <c r="E76" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>817</v>
+      </c>
+      <c r="B77" t="s">
+        <v>416</v>
+      </c>
+      <c r="D77" t="s">
+        <v>818</v>
+      </c>
+      <c r="E77" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>819</v>
+      </c>
+      <c r="B78" t="s">
+        <v>416</v>
+      </c>
+      <c r="D78" t="s">
+        <v>820</v>
+      </c>
+      <c r="E78" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>821</v>
+      </c>
+      <c r="B79" t="s">
+        <v>416</v>
+      </c>
+      <c r="D79" t="s">
+        <v>822</v>
+      </c>
+      <c r="E79" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>823</v>
+      </c>
+      <c r="B80" t="s">
+        <v>416</v>
+      </c>
+      <c r="D80" t="s">
+        <v>824</v>
+      </c>
+      <c r="E80" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>825</v>
+      </c>
+      <c r="B81" t="s">
+        <v>416</v>
+      </c>
+      <c r="D81" t="s">
+        <v>826</v>
+      </c>
+      <c r="E81" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>828</v>
+      </c>
+      <c r="B82" t="s">
+        <v>416</v>
+      </c>
+      <c r="D82" t="s">
+        <v>827</v>
+      </c>
+      <c r="E82" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>829</v>
+      </c>
+      <c r="B83" t="s">
+        <v>416</v>
+      </c>
+      <c r="D83" t="s">
+        <v>830</v>
+      </c>
+      <c r="E83" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>831</v>
+      </c>
+      <c r="B84" t="s">
+        <v>416</v>
+      </c>
+      <c r="D84" t="s">
+        <v>832</v>
+      </c>
+      <c r="E84" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>833</v>
+      </c>
+      <c r="B85" t="s">
+        <v>416</v>
+      </c>
+      <c r="D85" t="s">
+        <v>834</v>
+      </c>
+      <c r="E85" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>835</v>
+      </c>
+      <c r="B86" t="s">
+        <v>416</v>
+      </c>
+      <c r="D86" t="s">
+        <v>836</v>
+      </c>
+      <c r="E86" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>837</v>
+      </c>
+      <c r="B87" t="s">
+        <v>416</v>
+      </c>
+      <c r="D87" t="s">
+        <v>838</v>
+      </c>
+      <c r="E87" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>839</v>
+      </c>
+      <c r="B88" t="s">
+        <v>416</v>
+      </c>
+      <c r="D88" t="s">
+        <v>840</v>
+      </c>
+      <c r="E88" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>841</v>
+      </c>
+      <c r="B89" t="s">
+        <v>416</v>
+      </c>
+      <c r="D89" t="s">
+        <v>842</v>
+      </c>
+      <c r="E89" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>843</v>
+      </c>
+      <c r="B90" t="s">
+        <v>416</v>
+      </c>
+      <c r="D90" t="s">
+        <v>844</v>
+      </c>
+      <c r="E90" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>597</v>
+      </c>
+      <c r="B91" t="s">
+        <v>416</v>
+      </c>
+      <c r="D91" t="s">
+        <v>598</v>
+      </c>
+      <c r="E91" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>845</v>
+      </c>
+      <c r="B92" t="s">
+        <v>416</v>
+      </c>
+      <c r="D92" t="s">
+        <v>846</v>
+      </c>
+      <c r="E92" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>847</v>
+      </c>
+      <c r="B93" t="s">
+        <v>416</v>
+      </c>
+      <c r="D93" t="s">
+        <v>848</v>
+      </c>
+      <c r="E93" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="C102" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>342</v>
+      </c>
+      <c r="B104" t="s">
+        <v>419</v>
+      </c>
+      <c r="D104" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>340</v>
+      </c>
+      <c r="B105" t="s">
+        <v>419</v>
+      </c>
+      <c r="D105" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>337</v>
+      </c>
+      <c r="B106" t="s">
+        <v>419</v>
+      </c>
+      <c r="D106" s="18" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>344</v>
+      </c>
+      <c r="B107" t="s">
+        <v>419</v>
+      </c>
+      <c r="D107" t="s">
+        <v>426</v>
+      </c>
+      <c r="H107" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>345</v>
+      </c>
+      <c r="B109" t="s">
+        <v>166</v>
+      </c>
+      <c r="D109" t="s">
+        <v>435</v>
+      </c>
+      <c r="E109" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>335</v>
+      </c>
+      <c r="B110" t="s">
+        <v>166</v>
+      </c>
+      <c r="D110" t="s">
+        <v>414</v>
+      </c>
+      <c r="E110" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>338</v>
+      </c>
+      <c r="B111" t="s">
+        <v>166</v>
+      </c>
+      <c r="D111" t="s">
+        <v>420</v>
+      </c>
+      <c r="E111" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>313</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C112" s="19"/>
+      <c r="D112" t="s">
+        <v>492</v>
+      </c>
+      <c r="E112" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>446</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C113" s="19"/>
+      <c r="D113" t="s">
+        <v>445</v>
+      </c>
+      <c r="E113" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>346</v>
+      </c>
+      <c r="B114" t="s">
+        <v>166</v>
+      </c>
+      <c r="D114" t="s">
+        <v>436</v>
+      </c>
+      <c r="E114" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>311</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C115" s="19"/>
+      <c r="D115" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>322</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C116" s="19"/>
+      <c r="D116" t="s">
+        <v>488</v>
+      </c>
+      <c r="E116" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>327</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C117" s="19"/>
+      <c r="D117" t="s">
+        <v>487</v>
+      </c>
+      <c r="E117" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>309</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C118" s="19"/>
+      <c r="D118" t="s">
+        <v>498</v>
+      </c>
+      <c r="E118" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>310</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C119" s="19"/>
+      <c r="D119" t="s">
+        <v>500</v>
+      </c>
+      <c r="E119" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>509</v>
+      </c>
+      <c r="B120" t="s">
+        <v>166</v>
+      </c>
+      <c r="D120" t="s">
+        <v>510</v>
+      </c>
+      <c r="E120" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>315</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C121" s="19"/>
+      <c r="D121" t="s">
+        <v>497</v>
+      </c>
+      <c r="E121" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>558</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C122" t="s">
+        <v>557</v>
+      </c>
+      <c r="D122" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>560</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C123" t="s">
+        <v>557</v>
+      </c>
+      <c r="D123" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>562</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C124" t="s">
+        <v>557</v>
+      </c>
+      <c r="D124" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>565</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C125" t="s">
+        <v>564</v>
+      </c>
+      <c r="D125" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>567</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C126" t="s">
+        <v>564</v>
+      </c>
+      <c r="D126" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>569</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C127" t="s">
+        <v>570</v>
+      </c>
+      <c r="D127" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>573</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C128" t="s">
+        <v>572</v>
+      </c>
+      <c r="D128" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>574</v>
+      </c>
+      <c r="B129" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C129" t="s">
+        <v>572</v>
+      </c>
+      <c r="D129" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>578</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C130" t="s">
+        <v>572</v>
+      </c>
+      <c r="D130" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>580</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C131" t="s">
+        <v>579</v>
+      </c>
+      <c r="D131" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>583</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C132" t="s">
+        <v>582</v>
+      </c>
+      <c r="D132" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>585</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C133" t="s">
+        <v>582</v>
+      </c>
+      <c r="D133" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>587</v>
+      </c>
+      <c r="B134" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C134" t="s">
+        <v>582</v>
+      </c>
+      <c r="D134" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>590</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C135" t="s">
+        <v>589</v>
+      </c>
+      <c r="D135" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>593</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C136" t="s">
+        <v>589</v>
+      </c>
+      <c r="D136" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>595</v>
+      </c>
+      <c r="B137" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C137" t="s">
+        <v>594</v>
+      </c>
+      <c r="D137" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>597</v>
+      </c>
+      <c r="B138" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C138" t="s">
+        <v>594</v>
+      </c>
+      <c r="D138" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>599</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C139" t="s">
+        <v>594</v>
+      </c>
+      <c r="D139" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>602</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C140" t="s">
+        <v>601</v>
+      </c>
+      <c r="D140" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>605</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C141" t="s">
+        <v>604</v>
+      </c>
+      <c r="D141" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>607</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C142" t="s">
+        <v>604</v>
+      </c>
+      <c r="D142" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>610</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C143" t="s">
+        <v>609</v>
+      </c>
+      <c r="D143" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>335</v>
+      </c>
+      <c r="B144" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C144" t="s">
+        <v>609</v>
+      </c>
+      <c r="D144" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>613</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C145" t="s">
+        <v>612</v>
+      </c>
+      <c r="D145" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>615</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C146" t="s">
+        <v>612</v>
+      </c>
+      <c r="D146" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>617</v>
+      </c>
+      <c r="B147" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C147" t="s">
+        <v>612</v>
+      </c>
+      <c r="D147" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>619</v>
+      </c>
+      <c r="B148" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C148" t="s">
+        <v>612</v>
+      </c>
+      <c r="D148" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>621</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C149" t="s">
+        <v>623</v>
+      </c>
+      <c r="D149" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>625</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C150" t="s">
+        <v>624</v>
+      </c>
+      <c r="D150" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>627</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C151" t="s">
+        <v>624</v>
+      </c>
+      <c r="D151" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>630</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C152" t="s">
+        <v>629</v>
+      </c>
+      <c r="D152" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>632</v>
+      </c>
+      <c r="B153" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C153" t="s">
+        <v>629</v>
+      </c>
+      <c r="D153" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>635</v>
+      </c>
+      <c r="B154" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C154" t="s">
+        <v>634</v>
+      </c>
+      <c r="D154" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>637</v>
+      </c>
+      <c r="B155" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C155" t="s">
+        <v>634</v>
+      </c>
+      <c r="D155" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>639</v>
+      </c>
+      <c r="B156" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C156" t="s">
+        <v>634</v>
+      </c>
+      <c r="D156" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>641</v>
+      </c>
+      <c r="B157" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C157" t="s">
+        <v>634</v>
+      </c>
+      <c r="D157" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>643</v>
+      </c>
+      <c r="B158" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C158" t="s">
+        <v>644</v>
+      </c>
+      <c r="D158" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>646</v>
+      </c>
+      <c r="B159" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C159" t="s">
+        <v>644</v>
+      </c>
+      <c r="D159" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>648</v>
+      </c>
+      <c r="B160" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C160" t="s">
+        <v>644</v>
+      </c>
+      <c r="D160" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>651</v>
+      </c>
+      <c r="B161" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C161" t="s">
+        <v>650</v>
+      </c>
+      <c r="D161" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>653</v>
+      </c>
+      <c r="B162" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C162" t="s">
+        <v>650</v>
+      </c>
+      <c r="D162" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>656</v>
+      </c>
+      <c r="B163" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C163" t="s">
+        <v>655</v>
+      </c>
+      <c r="D163" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164" t="s">
+        <v>658</v>
+      </c>
+      <c r="B164" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C164" t="s">
+        <v>655</v>
+      </c>
+      <c r="D164" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165" t="s">
+        <v>661</v>
+      </c>
+      <c r="B165" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C165" t="s">
+        <v>660</v>
+      </c>
+      <c r="D165" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166" t="s">
+        <v>663</v>
+      </c>
+      <c r="B166" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C166" t="s">
+        <v>660</v>
+      </c>
+      <c r="D166" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A167" t="s">
+        <v>665</v>
+      </c>
+      <c r="B167" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C167" t="s">
+        <v>660</v>
+      </c>
+      <c r="D167" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168" t="s">
+        <v>667</v>
+      </c>
+      <c r="B168" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C168" t="s">
+        <v>669</v>
+      </c>
+      <c r="D168" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A169" t="s">
+        <v>671</v>
+      </c>
+      <c r="B169" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C169" t="s">
+        <v>669</v>
+      </c>
+      <c r="D169" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B170" s="19"/>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D174" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A176" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A177" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A178" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A179" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A180" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A181" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A193" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A194" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A195" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A196" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A197" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A198" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A199" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A200" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A201" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A202" t="s">
+        <v>550</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D119">
+    <sortCondition descending="1" ref="B2:B119"/>
+  </sortState>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2651,30 +7736,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2706,17 +7791,17 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
     </row>
     <row r="6" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
@@ -2854,17 +7939,17 @@
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
     </row>
     <row r="12" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
@@ -3002,17 +8087,17 @@
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
@@ -3150,17 +8235,17 @@
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
     </row>
     <row r="24" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
@@ -3298,17 +8383,17 @@
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
     </row>
     <row r="30" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
@@ -3446,17 +8531,17 @@
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
     </row>
     <row r="36" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
@@ -3609,2030 +8694,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C59208D-E153-D94F-949B-1D2F26D7FF23}">
-  <dimension ref="A1:I163"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="58" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="23.6640625" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.5" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="D1" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>554</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>453</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C2" s="19"/>
-      <c r="D2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F2" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>306</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C3" s="19"/>
-      <c r="D3" t="s">
-        <v>429</v>
-      </c>
-      <c r="E3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>339</v>
-      </c>
-      <c r="B4" t="s">
-        <v>416</v>
-      </c>
-      <c r="D4" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>441</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C5" s="19"/>
-      <c r="D5" t="s">
-        <v>460</v>
-      </c>
-      <c r="E5" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>464</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C6" s="19"/>
-      <c r="D6" t="s">
-        <v>467</v>
-      </c>
-      <c r="E6" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>336</v>
-      </c>
-      <c r="B7" t="s">
-        <v>416</v>
-      </c>
-      <c r="D7" t="s">
-        <v>417</v>
-      </c>
-      <c r="E7" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>333</v>
-      </c>
-      <c r="B8" t="s">
-        <v>416</v>
-      </c>
-      <c r="D8" t="s">
-        <v>412</v>
-      </c>
-      <c r="E8" t="s">
-        <v>557</v>
-      </c>
-      <c r="H8" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>349</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C9" s="19"/>
-      <c r="D9" t="s">
-        <v>439</v>
-      </c>
-      <c r="E9" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>347</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C10" s="19"/>
-      <c r="D10" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>470</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" t="s">
-        <v>471</v>
-      </c>
-      <c r="F11" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>458</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" t="s">
-        <v>459</v>
-      </c>
-      <c r="F12" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>320</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" t="s">
-        <v>457</v>
-      </c>
-      <c r="E13" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>341</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" t="s">
-        <v>423</v>
-      </c>
-      <c r="E14" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>301</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" t="s">
-        <v>427</v>
-      </c>
-      <c r="H15" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>330</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" t="s">
-        <v>496</v>
-      </c>
-      <c r="E16" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>324</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C17" s="19"/>
-      <c r="D17" t="s">
-        <v>495</v>
-      </c>
-      <c r="E17" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>455</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C18" s="19"/>
-      <c r="D18" t="s">
-        <v>456</v>
-      </c>
-      <c r="F18" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>300</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C19" s="19"/>
-      <c r="D19" t="s">
-        <v>490</v>
-      </c>
-      <c r="E19" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>332</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C20" s="19"/>
-      <c r="D20" t="s">
-        <v>494</v>
-      </c>
-      <c r="E20" t="s">
-        <v>557</v>
-      </c>
-      <c r="I20" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>303</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C21" s="19"/>
-      <c r="D21" t="s">
-        <v>493</v>
-      </c>
-      <c r="E21" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>446</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="D22" t="s">
-        <v>445</v>
-      </c>
-      <c r="E22" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>328</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C23" s="19"/>
-      <c r="D23" t="s">
-        <v>433</v>
-      </c>
-      <c r="E23" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>350</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C24" s="19"/>
-      <c r="D24" t="s">
-        <v>440</v>
-      </c>
-      <c r="E24" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>474</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" t="s">
-        <v>475</v>
-      </c>
-      <c r="E25" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>348</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>447</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" t="s">
-        <v>448</v>
-      </c>
-      <c r="E27" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>468</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" t="s">
-        <v>469</v>
-      </c>
-      <c r="E28" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>343</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" t="s">
-        <v>425</v>
-      </c>
-      <c r="E29" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>472</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" t="s">
-        <v>473</v>
-      </c>
-      <c r="E30" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>478</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="D31" t="s">
-        <v>477</v>
-      </c>
-      <c r="E31" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>323</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" t="s">
-        <v>432</v>
-      </c>
-      <c r="E32" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>317</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="D33" t="s">
-        <v>489</v>
-      </c>
-      <c r="E33" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>465</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" t="s">
-        <v>466</v>
-      </c>
-      <c r="E34" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>308</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" t="s">
-        <v>431</v>
-      </c>
-      <c r="G35" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>331</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="D36" t="s">
-        <v>434</v>
-      </c>
-      <c r="E36" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>298</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="D37" t="s">
-        <v>486</v>
-      </c>
-      <c r="E37" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>312</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C38" s="19"/>
-      <c r="D38" t="s">
-        <v>485</v>
-      </c>
-      <c r="E38" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>299</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="D39" t="s">
-        <v>484</v>
-      </c>
-      <c r="E39" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>314</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C40" s="19"/>
-      <c r="D40" t="s">
-        <v>483</v>
-      </c>
-      <c r="E40" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>449</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" t="s">
-        <v>450</v>
-      </c>
-      <c r="E41" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>334</v>
-      </c>
-      <c r="B42" t="s">
-        <v>416</v>
-      </c>
-      <c r="D42" t="s">
-        <v>413</v>
-      </c>
-      <c r="E42" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>443</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C43" s="19"/>
-      <c r="D43" t="s">
-        <v>444</v>
-      </c>
-      <c r="E43" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>442</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C44" s="19"/>
-      <c r="D44" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>451</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C45" s="19"/>
-      <c r="D45" t="s">
-        <v>452</v>
-      </c>
-      <c r="E45" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>318</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C46" s="19"/>
-      <c r="D46" t="s">
-        <v>482</v>
-      </c>
-      <c r="E46" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>326</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C47" s="19"/>
-      <c r="D47" t="s">
-        <v>481</v>
-      </c>
-      <c r="E47" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>329</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C48" s="19"/>
-      <c r="D48" t="s">
-        <v>480</v>
-      </c>
-      <c r="E48" t="s">
-        <v>558</v>
-      </c>
-      <c r="F48" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>462</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C49" s="19"/>
-      <c r="D49" t="s">
-        <v>463</v>
-      </c>
-      <c r="E49" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>302</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C50" s="19"/>
-      <c r="D50" t="s">
-        <v>428</v>
-      </c>
-      <c r="E50" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>325</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C51" s="19"/>
-      <c r="D51" t="s">
-        <v>479</v>
-      </c>
-      <c r="E51" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>307</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C52" s="19"/>
-      <c r="D52" t="s">
-        <v>430</v>
-      </c>
-      <c r="E52" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>316</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C53" s="19"/>
-      <c r="D53" t="s">
-        <v>499</v>
-      </c>
-      <c r="E53" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>319</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C54" s="19"/>
-      <c r="D54" t="s">
-        <v>501</v>
-      </c>
-      <c r="E54" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>321</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C55" s="19"/>
-      <c r="D55" t="s">
-        <v>502</v>
-      </c>
-      <c r="E55" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>305</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C56" s="19"/>
-      <c r="D56" t="s">
-        <v>503</v>
-      </c>
-      <c r="E56" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>304</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="C57" s="19"/>
-      <c r="D57" t="s">
-        <v>504</v>
-      </c>
-      <c r="E57" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>517</v>
-      </c>
-      <c r="B58" t="s">
-        <v>416</v>
-      </c>
-      <c r="D58" t="s">
-        <v>518</v>
-      </c>
-      <c r="E58" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>519</v>
-      </c>
-      <c r="B59" t="s">
-        <v>416</v>
-      </c>
-      <c r="D59" t="s">
-        <v>520</v>
-      </c>
-      <c r="E59" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>521</v>
-      </c>
-      <c r="B60" t="s">
-        <v>416</v>
-      </c>
-      <c r="D60" t="s">
-        <v>522</v>
-      </c>
-      <c r="E60" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>523</v>
-      </c>
-      <c r="B61" t="s">
-        <v>416</v>
-      </c>
-      <c r="D61" t="s">
-        <v>524</v>
-      </c>
-      <c r="E61" t="s">
-        <v>558</v>
-      </c>
-      <c r="H61" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>507</v>
-      </c>
-      <c r="B62" t="s">
-        <v>416</v>
-      </c>
-      <c r="D62" t="s">
-        <v>508</v>
-      </c>
-      <c r="E62" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>511</v>
-      </c>
-      <c r="B63" t="s">
-        <v>416</v>
-      </c>
-      <c r="D63" t="s">
-        <v>512</v>
-      </c>
-      <c r="E63" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>513</v>
-      </c>
-      <c r="B64" t="s">
-        <v>416</v>
-      </c>
-      <c r="D64" t="s">
-        <v>514</v>
-      </c>
-      <c r="E64" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>516</v>
-      </c>
-      <c r="B65" t="s">
-        <v>416</v>
-      </c>
-      <c r="D65" t="s">
-        <v>515</v>
-      </c>
-      <c r="E65" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>342</v>
-      </c>
-      <c r="B67" t="s">
-        <v>419</v>
-      </c>
-      <c r="D67" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>340</v>
-      </c>
-      <c r="B68" t="s">
-        <v>419</v>
-      </c>
-      <c r="D68" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>337</v>
-      </c>
-      <c r="B69" t="s">
-        <v>419</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>344</v>
-      </c>
-      <c r="B70" t="s">
-        <v>419</v>
-      </c>
-      <c r="D70" t="s">
-        <v>426</v>
-      </c>
-      <c r="H70" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>345</v>
-      </c>
-      <c r="B72" t="s">
-        <v>166</v>
-      </c>
-      <c r="D72" t="s">
-        <v>435</v>
-      </c>
-      <c r="E72" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>335</v>
-      </c>
-      <c r="B73" t="s">
-        <v>166</v>
-      </c>
-      <c r="D73" t="s">
-        <v>414</v>
-      </c>
-      <c r="E73" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>338</v>
-      </c>
-      <c r="B74" t="s">
-        <v>166</v>
-      </c>
-      <c r="D74" t="s">
-        <v>420</v>
-      </c>
-      <c r="E74" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>313</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C75" s="19"/>
-      <c r="D75" t="s">
-        <v>492</v>
-      </c>
-      <c r="E75" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
-        <v>446</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C76" s="19"/>
-      <c r="D76" t="s">
-        <v>445</v>
-      </c>
-      <c r="E76" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
-        <v>346</v>
-      </c>
-      <c r="B77" t="s">
-        <v>166</v>
-      </c>
-      <c r="D77" t="s">
-        <v>436</v>
-      </c>
-      <c r="E77" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
-        <v>311</v>
-      </c>
-      <c r="B78" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C78" s="19"/>
-      <c r="D78" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>322</v>
-      </c>
-      <c r="B79" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C79" s="19"/>
-      <c r="D79" t="s">
-        <v>488</v>
-      </c>
-      <c r="E79" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
-        <v>327</v>
-      </c>
-      <c r="B80" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C80" s="19"/>
-      <c r="D80" t="s">
-        <v>487</v>
-      </c>
-      <c r="E80" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>309</v>
-      </c>
-      <c r="B81" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C81" s="19"/>
-      <c r="D81" t="s">
-        <v>498</v>
-      </c>
-      <c r="E81" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
-        <v>310</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C82" s="19"/>
-      <c r="D82" t="s">
-        <v>500</v>
-      </c>
-      <c r="E82" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
-        <v>509</v>
-      </c>
-      <c r="B83" t="s">
-        <v>166</v>
-      </c>
-      <c r="D83" t="s">
-        <v>510</v>
-      </c>
-      <c r="E83" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
-        <v>315</v>
-      </c>
-      <c r="B84" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C84" s="19"/>
-      <c r="D84" t="s">
-        <v>497</v>
-      </c>
-      <c r="E84" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
-        <v>561</v>
-      </c>
-      <c r="B85" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C85" t="s">
-        <v>560</v>
-      </c>
-      <c r="D85" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
-        <v>563</v>
-      </c>
-      <c r="B86" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C86" t="s">
-        <v>560</v>
-      </c>
-      <c r="D86" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
-        <v>565</v>
-      </c>
-      <c r="B87" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C87" t="s">
-        <v>560</v>
-      </c>
-      <c r="D87" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>568</v>
-      </c>
-      <c r="B88" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C88" t="s">
-        <v>567</v>
-      </c>
-      <c r="D88" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>570</v>
-      </c>
-      <c r="B89" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C89" t="s">
-        <v>567</v>
-      </c>
-      <c r="D89" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A90" t="s">
-        <v>572</v>
-      </c>
-      <c r="B90" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C90" t="s">
-        <v>573</v>
-      </c>
-      <c r="D90" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
-        <v>576</v>
-      </c>
-      <c r="B91" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C91" t="s">
-        <v>575</v>
-      </c>
-      <c r="D91" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
-        <v>577</v>
-      </c>
-      <c r="B92" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C92" t="s">
-        <v>575</v>
-      </c>
-      <c r="D92" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
-        <v>581</v>
-      </c>
-      <c r="B93" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C93" t="s">
-        <v>575</v>
-      </c>
-      <c r="D93" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
-        <v>583</v>
-      </c>
-      <c r="B94" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C94" t="s">
-        <v>582</v>
-      </c>
-      <c r="D94" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>586</v>
-      </c>
-      <c r="B95" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C95" t="s">
-        <v>585</v>
-      </c>
-      <c r="D95" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>588</v>
-      </c>
-      <c r="B96" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C96" t="s">
-        <v>585</v>
-      </c>
-      <c r="D96" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
-        <v>590</v>
-      </c>
-      <c r="B97" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C97" t="s">
-        <v>585</v>
-      </c>
-      <c r="D97" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>593</v>
-      </c>
-      <c r="B98" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C98" t="s">
-        <v>592</v>
-      </c>
-      <c r="D98" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
-        <v>596</v>
-      </c>
-      <c r="B99" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C99" t="s">
-        <v>592</v>
-      </c>
-      <c r="D99" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="32" t="s">
-        <v>598</v>
-      </c>
-      <c r="B100" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C100" t="s">
-        <v>597</v>
-      </c>
-      <c r="D100" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="32" t="s">
-        <v>600</v>
-      </c>
-      <c r="B101" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C101" t="s">
-        <v>597</v>
-      </c>
-      <c r="D101" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="32" t="s">
-        <v>602</v>
-      </c>
-      <c r="B102" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C102" t="s">
-        <v>597</v>
-      </c>
-      <c r="D102" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>605</v>
-      </c>
-      <c r="B103" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C103" t="s">
-        <v>604</v>
-      </c>
-      <c r="D103" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>608</v>
-      </c>
-      <c r="B104" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C104" t="s">
-        <v>607</v>
-      </c>
-      <c r="D104" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>610</v>
-      </c>
-      <c r="B105" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C105" t="s">
-        <v>607</v>
-      </c>
-      <c r="D105" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>613</v>
-      </c>
-      <c r="B106" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C106" t="s">
-        <v>612</v>
-      </c>
-      <c r="D106" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
-        <v>335</v>
-      </c>
-      <c r="B107" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C107" t="s">
-        <v>612</v>
-      </c>
-      <c r="D107" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
-        <v>616</v>
-      </c>
-      <c r="B108" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C108" t="s">
-        <v>615</v>
-      </c>
-      <c r="D108" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
-        <v>618</v>
-      </c>
-      <c r="B109" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C109" t="s">
-        <v>615</v>
-      </c>
-      <c r="D109" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>620</v>
-      </c>
-      <c r="B110" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C110" t="s">
-        <v>615</v>
-      </c>
-      <c r="D110" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>622</v>
-      </c>
-      <c r="B111" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C111" t="s">
-        <v>615</v>
-      </c>
-      <c r="D111" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>624</v>
-      </c>
-      <c r="B112" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C112" t="s">
-        <v>626</v>
-      </c>
-      <c r="D112" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
-        <v>628</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C113" t="s">
-        <v>627</v>
-      </c>
-      <c r="D113" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>630</v>
-      </c>
-      <c r="B114" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C114" t="s">
-        <v>627</v>
-      </c>
-      <c r="D114" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>633</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C115" t="s">
-        <v>632</v>
-      </c>
-      <c r="D115" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
-        <v>635</v>
-      </c>
-      <c r="B116" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C116" t="s">
-        <v>632</v>
-      </c>
-      <c r="D116" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>638</v>
-      </c>
-      <c r="B117" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C117" t="s">
-        <v>637</v>
-      </c>
-      <c r="D117" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>640</v>
-      </c>
-      <c r="B118" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C118" t="s">
-        <v>637</v>
-      </c>
-      <c r="D118" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
-        <v>642</v>
-      </c>
-      <c r="B119" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C119" t="s">
-        <v>637</v>
-      </c>
-      <c r="D119" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
-        <v>644</v>
-      </c>
-      <c r="B120" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C120" t="s">
-        <v>637</v>
-      </c>
-      <c r="D120" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
-        <v>646</v>
-      </c>
-      <c r="B121" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C121" t="s">
-        <v>647</v>
-      </c>
-      <c r="D121" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
-        <v>649</v>
-      </c>
-      <c r="B122" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C122" t="s">
-        <v>647</v>
-      </c>
-      <c r="D122" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
-        <v>651</v>
-      </c>
-      <c r="B123" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C123" t="s">
-        <v>647</v>
-      </c>
-      <c r="D123" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
-        <v>654</v>
-      </c>
-      <c r="B124" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C124" t="s">
-        <v>653</v>
-      </c>
-      <c r="D124" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
-        <v>656</v>
-      </c>
-      <c r="B125" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C125" t="s">
-        <v>653</v>
-      </c>
-      <c r="D125" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
-        <v>659</v>
-      </c>
-      <c r="B126" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C126" t="s">
-        <v>658</v>
-      </c>
-      <c r="D126" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
-        <v>661</v>
-      </c>
-      <c r="B127" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C127" t="s">
-        <v>658</v>
-      </c>
-      <c r="D127" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128" s="32" t="s">
-        <v>664</v>
-      </c>
-      <c r="B128" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C128" t="s">
-        <v>663</v>
-      </c>
-      <c r="D128" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
-        <v>666</v>
-      </c>
-      <c r="B129" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C129" t="s">
-        <v>663</v>
-      </c>
-      <c r="D129" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130" s="32" t="s">
-        <v>668</v>
-      </c>
-      <c r="B130" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C130" t="s">
-        <v>663</v>
-      </c>
-      <c r="D130" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B131" s="19"/>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A134" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A135" t="s">
-        <v>532</v>
-      </c>
-      <c r="D135" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A136" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A137" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A138" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A139" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A140" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A141" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A142" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A143" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A144" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A145" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A146" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A147" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A148" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A149" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A150" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A151" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A152" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A153" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A154" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A155" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A160" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A161" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A162" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A163" t="s">
-        <v>553</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D82">
-    <sortCondition descending="1" ref="B2:B82"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5650,40 +8712,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
     </row>
     <row r="4" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -7701,7 +10763,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -7712,23 +10774,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="31"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="21"/>
+      <c r="B4" s="30"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -7740,10 +10802,10 @@
       </c>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="21"/>
+      <c r="B8" s="30"/>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
@@ -7762,10 +10824,10 @@
       </c>
     </row>
     <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="B12" s="21"/>
+      <c r="B12" s="30"/>
     </row>
     <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
@@ -7784,10 +10846,10 @@
       </c>
     </row>
     <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="B16" s="21"/>
+      <c r="B16" s="30"/>
     </row>
     <row r="17" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
@@ -7802,14 +10864,14 @@
         <v>193</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="B20" s="21"/>
+      <c r="B20" s="30"/>
     </row>
     <row r="21" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
@@ -7820,18 +10882,18 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="35" t="s">
         <v>351</v>
       </c>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="36" t="s">
         <v>352</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B27" s="14" t="s">
@@ -7842,11 +10904,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="30" t="s">
         <v>355</v>
       </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
     </row>
     <row r="29" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
@@ -7871,11 +10933,11 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="30" t="s">
         <v>360</v>
       </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
     </row>
     <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
@@ -7900,11 +10962,11 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="30" t="s">
         <v>365</v>
       </c>
-      <c r="B36" s="21"/>
-      <c r="C36" s="21"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
     </row>
     <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
@@ -7929,11 +10991,11 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="30" t="s">
         <v>370</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
     </row>
     <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
@@ -7958,11 +11020,11 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="30" t="s">
         <v>374</v>
       </c>
-      <c r="B44" s="21"/>
-      <c r="C44" s="21"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
     </row>
     <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
@@ -8007,7 +11069,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8020,13 +11082,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -8341,24 +11403,24 @@
       <c r="E45" s="6"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="26" t="s">
+      <c r="A47" s="37" t="s">
         <v>205</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="D47" s="26" t="s">
+      <c r="B47" s="37"/>
+      <c r="D47" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="E47" s="26"/>
+      <c r="E47" s="37"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="27" t="s">
+      <c r="A48" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="B48" s="27"/>
-      <c r="D48" s="27" t="s">
+      <c r="B48" s="38"/>
+      <c r="D48" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="E48" s="27"/>
+      <c r="E48" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -8373,7 +11435,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8383,17 +11445,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -8725,17 +11787,17 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -8747,7 +11809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8760,15 +11822,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -8963,7 +12025,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D9436A-E997-3C40-A694-C3E3FD008A15}">
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -8976,24 +12038,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="34" t="s">
         <v>379</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
@@ -9230,7 +12292,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -9241,18 +12303,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="31" t="s">
         <v>280</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="41" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -9309,252 +12371,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:C45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="46" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
-        <v>293</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>
--- a/sendcleared-outreach-tracker.xlsx
+++ b/sendcleared-outreach-tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timothyarmstead/Sendcleared/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8B207A-B42F-9746-893D-810316C03EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86844F5E-9339-5946-9B12-A4546D95B2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3320" yWindow="600" windowWidth="27860" windowHeight="16220" tabRatio="500" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8980" yWindow="1740" windowWidth="27860" windowHeight="16220" tabRatio="500" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="12" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1363" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="868">
   <si>
     <t>SendCleared — Daily Outreach Playbook  |  1 Hour / Day</t>
   </si>
@@ -2660,6 +2660,130 @@
   </si>
   <si>
     <t>15.09.26</t>
+  </si>
+  <si>
+    <t>"What is the worst email marketing mistake you've ever made or seen?"</t>
+  </si>
+  <si>
+    <r>
+      <t>"How do you prevent sending an email with broken links or bad merge tags (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>{{first_name}}</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>)?"</t>
+    </r>
+  </si>
+  <si>
+    <t>"Why do my HTML emails look broken in Outlook or Apple Mail?"</t>
+  </si>
+  <si>
+    <t>Pre-Send Process &amp; Checklists</t>
+  </si>
+  <si>
+    <t>"What is your pre-launch checklist before hitting 'Send' on an email campaign?"</t>
+  </si>
+  <si>
+    <t>"How do email marketers perform QA on automated lifecycle flows (Klaviyo, HubSpot, etc.)?"</t>
+  </si>
+  <si>
+    <t>"What is the best way to double-check email render and formatting across different clients?"</t>
+  </si>
+  <si>
+    <t>Tooling &amp; Alternatives</t>
+  </si>
+  <si>
+    <t>"Are there any good alternative tools to Litmus or Email on Acid for email QA testing?"</t>
+  </si>
+  <si>
+    <t>"What are the best automated tools to catch email bugs before broadcast?"</t>
+  </si>
+  <si>
+    <t>"How do you test dark mode rendering for HTML email newsletters?"</t>
+  </si>
+  <si>
+    <t>Strategy to Plug SendCleared on Quora</t>
+  </si>
+  <si>
+    <r>
+      <t>Provide a High-Value Framework First:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Don't just post a sales link. Give a structured 4-point manual checklist (e.g., checking subject lines/preheaders, testing live fallback tags, rendering on mobile/dark mode, verifying preview texts).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Introduce the "Automated Solution":</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Explain that doing manual checks across every broadcast or automation update takes 15–20 minutes and still leaves room for human error.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Soft Pitch:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>"To speed this up and catch things like broken dynamic tags or broken layouts automatically, tools like SendCleared run these pre-flight checks instantly before you send."</t>
+    </r>
+  </si>
+  <si>
+    <t>Common QA Failures &amp; Disaster Stories - Quora - Target email marketing category - will need to keep broad</t>
+  </si>
+  <si>
+    <t>Second Send</t>
+  </si>
+  <si>
+    <t>16.09.26</t>
   </si>
 </sst>
 </file>
@@ -2670,7 +2794,7 @@
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yy"/>
     <numFmt numFmtId="165" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2805,6 +2929,29 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -2889,7 +3036,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2975,6 +3122,8 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5286,7 +5435,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C59208D-E153-D94F-949B-1D2F26D7FF23}">
-  <dimension ref="A1:I202"/>
+  <dimension ref="A1:J202"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58" customWidth="1"/>
@@ -5316,6 +5465,9 @@
       <c r="F1" s="20" t="s">
         <v>553</v>
       </c>
+      <c r="G1" s="20" t="s">
+        <v>866</v>
+      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
@@ -5346,6 +5498,9 @@
       <c r="E3" t="s">
         <v>554</v>
       </c>
+      <c r="G3" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -5372,6 +5527,9 @@
       <c r="E5" t="s">
         <v>554</v>
       </c>
+      <c r="G5" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -5387,6 +5545,9 @@
       <c r="E6" t="s">
         <v>554</v>
       </c>
+      <c r="G6" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -5401,6 +5562,9 @@
       <c r="E7" t="s">
         <v>554</v>
       </c>
+      <c r="G7" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -5415,6 +5579,9 @@
       <c r="E8" t="s">
         <v>554</v>
       </c>
+      <c r="G8" t="s">
+        <v>867</v>
+      </c>
       <c r="H8" t="s">
         <v>476</v>
       </c>
@@ -5433,6 +5600,9 @@
       <c r="E9" t="s">
         <v>554</v>
       </c>
+      <c r="G9" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -5460,6 +5630,9 @@
       <c r="F11" t="s">
         <v>554</v>
       </c>
+      <c r="G11" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -5475,6 +5648,9 @@
       <c r="F12" t="s">
         <v>554</v>
       </c>
+      <c r="G12" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -5490,6 +5666,9 @@
       <c r="E13" t="s">
         <v>554</v>
       </c>
+      <c r="G13" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -5505,6 +5684,9 @@
       <c r="E14" t="s">
         <v>554</v>
       </c>
+      <c r="G14" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -5535,8 +5717,11 @@
       <c r="E16" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G16" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>324</v>
       </c>
@@ -5550,8 +5735,11 @@
       <c r="E17" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G17" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>455</v>
       </c>
@@ -5565,8 +5753,14 @@
       <c r="F18" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G18" t="s">
+        <v>867</v>
+      </c>
+      <c r="J18" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>300</v>
       </c>
@@ -5580,8 +5774,11 @@
       <c r="E19" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G19" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>332</v>
       </c>
@@ -5595,11 +5792,14 @@
       <c r="E20" t="s">
         <v>554</v>
       </c>
+      <c r="G20" t="s">
+        <v>867</v>
+      </c>
       <c r="I20" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>303</v>
       </c>
@@ -5613,8 +5813,11 @@
       <c r="E21" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G21" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>446</v>
       </c>
@@ -5629,7 +5832,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>328</v>
       </c>
@@ -5643,8 +5846,11 @@
       <c r="E23" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G23" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>350</v>
       </c>
@@ -5658,8 +5864,11 @@
       <c r="E24" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G24" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>474</v>
       </c>
@@ -5673,8 +5882,11 @@
       <c r="E25" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G25" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>348</v>
       </c>
@@ -5686,7 +5898,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>447</v>
       </c>
@@ -5700,8 +5912,11 @@
       <c r="E27" t="s">
         <v>554</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G27" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>468</v>
       </c>
@@ -5716,7 +5931,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>343</v>
       </c>
@@ -5731,7 +5946,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>472</v>
       </c>
@@ -5746,7 +5961,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>478</v>
       </c>
@@ -5761,7 +5976,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>323</v>
       </c>
@@ -12294,7 +12509,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -12363,6 +12578,86 @@
       </c>
       <c r="C8" s="6"/>
     </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="43" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="44" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.25">
+      <c r="A14" s="44" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="44" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="43" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="44" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="44" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="44" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="43" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="44" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="44" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="44" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="43" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="43" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="43" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="43" t="s">
+        <v>864</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>

--- a/sendcleared-outreach-tracker.xlsx
+++ b/sendcleared-outreach-tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timothyarmstead/Sendcleared/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86844F5E-9339-5946-9B12-A4546D95B2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B07565C-6D78-DA4D-8548-8C78A9FC9B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8980" yWindow="1740" windowWidth="27860" windowHeight="16220" tabRatio="500" firstSheet="3" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39220" yWindow="4860" windowWidth="27860" windowHeight="16220" tabRatio="500" firstSheet="4" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="12" r:id="rId1"/>
@@ -24,10 +24,11 @@
     <sheet name="Community Questions" sheetId="7" r:id="rId9"/>
     <sheet name="SEO Content Plan" sheetId="11" r:id="rId10"/>
     <sheet name="Community Posts" sheetId="8" r:id="rId11"/>
-    <sheet name="Contacts " sheetId="9" r:id="rId12"/>
+    <sheet name="Directory Listings" sheetId="13" r:id="rId12"/>
+    <sheet name="Contacts " sheetId="9" r:id="rId13"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId13"/>
+    <externalReference r:id="rId14"/>
   </externalReferences>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="918">
   <si>
     <t>SendCleared — Daily Outreach Playbook  |  1 Hour / Day</t>
   </si>
@@ -2105,12 +2106,6 @@
   </si>
   <si>
     <t>Chloe L</t>
-  </si>
-  <si>
-    <t>https://www.linkedin.com/in/spencer-moore-37a993245/</t>
-  </si>
-  <si>
-    <t>Spencer Moore</t>
   </si>
   <si>
     <t>https://www.linkedin.com/in/saad-chaudhry-/</t>
@@ -2785,6 +2780,312 @@
   <si>
     <t>16.09.26</t>
   </si>
+  <si>
+    <t>https://www.linkedin.com/in/valeriarobles24/</t>
+  </si>
+  <si>
+    <t>Valeria Robles</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kristi-treder-7289965/</t>
+  </si>
+  <si>
+    <t>Kristi Treder</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/nikoloz-saralidze-2314b8154/</t>
+  </si>
+  <si>
+    <t>Nikoloz Saralidze</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/victor-bizuett-6a954991/?locale=en</t>
+  </si>
+  <si>
+    <t>Victor Bizuett</t>
+  </si>
+  <si>
+    <t>Denas Kuliničius</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/denaskulinicius/</t>
+  </si>
+  <si>
+    <t>Taylor Lumpkin</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/taylorlumpkin/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/klaviyo-expert/</t>
+  </si>
+  <si>
+    <t>Ryan Turner</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/rr-chris-lawbuary/</t>
+  </si>
+  <si>
+    <t>Chris Lawbuary</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/gnegrin/</t>
+  </si>
+  <si>
+    <t>Gabriel Negrín</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/barbarabsantos/</t>
+  </si>
+  <si>
+    <t>Bárbara Santos</t>
+  </si>
+  <si>
+    <t>Tier 1 — high-authority, worth the effort (submit in week 1)</t>
+  </si>
+  <si>
+    <t>Directory</t>
+  </si>
+  <si>
+    <t>Why it matters</t>
+  </si>
+  <si>
+    <t>Product Hunt</t>
+  </si>
+  <si>
+    <t>The single biggest traffic spike opportunity; treat launch day as an event, not a passive listing</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>List under "Email Testing Software" — the same category Litmus and Email on Acid sit in, so you're in front of people actively comparing</t>
+  </si>
+  <si>
+    <t>Capterra</t>
+  </si>
+  <si>
+    <t>Same category-matching logic as G2; Gartner-owned, high buyer trust</t>
+  </si>
+  <si>
+    <t>GetApp</t>
+  </si>
+  <si>
+    <t>Also Gartner-family — same listing content works across all three with minor edits</t>
+  </si>
+  <si>
+    <t>AlternativeTo</t>
+  </si>
+  <si>
+    <t>Directly relevant given your comparison-page strategy — list Litmus and Email on Acid as the tools SendCleared is an alternative to</t>
+  </si>
+  <si>
+    <t>Crunchbase</t>
+  </si>
+  <si>
+    <t>Less about traffic, more about legitimacy signal for anyone researching the company</t>
+  </si>
+  <si>
+    <t>SaaSHub</t>
+  </si>
+  <si>
+    <t>Good DR, accepts "alternative to X" framing directly</t>
+  </si>
+  <si>
+    <t>Tier 2 — fast, free, low-effort dofollow listings (batch these, 3–5/day)</t>
+  </si>
+  <si>
+    <r>
+      <t>Indie Hackers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — also worth being </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>active</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> in, not just listed; your build-in-public content already fits this audience</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BetaList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — less relevant now you're past pre-launch, but still worth a listing for backlink value</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>StackShare</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — more dev-tool-oriented, lower priority but easy</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>F6S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — startup-focused, decent authority</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Smol Launch / Launching Next / DevHunt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — modern, curated, genuinely free dofollow links; good ROI for the time cost</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Avoid:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> mass-submission/auto-approval services (PRLog, EzineArticles-style, or anyone offering "300 directories in a day") — these are flagged as actively harmful to domain authority now, not just low-value.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tier 3 — niche fit for your specific audience</t>
+  </si>
+  <si>
+    <r>
+      <t>AppSumo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — lifetime-deal marketplace; strong fit since your audience (freelancers, small agencies) is exactly who browses there, but worth thinking through the trade-off: LTD revenue is a one-time hit that can undercut your recurring MRR model. Worth a deliberate decision, not a default yes.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Klaviyo App Marketplace / Integrations directory</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>Mailchimp equivalent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — these are the highest-intent placements possible given your actual ICP, but they typically require a formal technical integration/certification process, not just a listing form. Flag this as a "pursue once you have engineering time," not a quick win.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Show HN (Hacker News)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> — not a directory, but a free "Show HN: SendCleared" post at launch or a major update can be genuinely high-leverage if it lands — technical/founder audience, thousands of eyes if it catches on. Zero cost to try.</t>
+    </r>
+  </si>
+  <si>
+    <t>22.09.26</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>No Connected</t>
+  </si>
+  <si>
+    <t>23.09.26</t>
+  </si>
 </sst>
 </file>
 
@@ -2794,7 +3095,7 @@
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yy"/>
     <numFmt numFmtId="165" formatCode="dd\ mmm\ yyyy"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2952,8 +3253,16 @@
       <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3008,6 +3317,12 @@
         <bgColor rgb="FFF7F7F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -3036,7 +3351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -3101,13 +3416,15 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3122,8 +3439,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4179,28 +4502,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="23" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
-        <v>743</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
+      <c r="A1" s="32" t="s">
+        <v>741</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34" t="s">
-        <v>744</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="A2" s="33" t="s">
+        <v>742</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B4" s="27">
         <v>46261</v>
@@ -4208,98 +4531,98 @@
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B5" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B6" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="28" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>755</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>756</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
+        <v>756</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>757</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>758</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="D11" s="17" t="s">
         <v>759</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>760</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>763</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>764</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="17" t="s">
+        <v>764</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>765</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>766</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="D13" s="17" t="s">
         <v>767</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>768</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="28" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -4307,70 +4630,70 @@
         <v>2</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>773</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
+        <v>774</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>775</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>776</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>777</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>779</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
+        <v>780</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>781</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>782</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>783</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>785</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>786</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="28" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
@@ -4378,12 +4701,12 @@
         <v>210</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B27" s="6">
         <f>COUNTA('[1]Daily Plan'!F2:F200)</f>
@@ -4392,7 +4715,7 @@
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B28" s="16" t="e">
         <f>COUNTIF('[1]Daily Plan'!H2:H200,"Done")</f>
@@ -4401,7 +4724,7 @@
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B29" s="6" t="e">
         <f>COUNTIF('[1]Daily Plan'!H2:H200,"In progress")</f>
@@ -4410,7 +4733,7 @@
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B30" s="16" t="e">
         <f>COUNTIF('[1]Daily Plan'!H2:H200,"Not started")</f>
@@ -4419,7 +4742,7 @@
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B31" s="29">
         <f>IFERROR(B28/B27,0)</f>
@@ -4452,28 +4775,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
-        <v>672</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
+      <c r="A1" s="42" t="s">
+        <v>670</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34" t="s">
-        <v>673</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="A2" s="33" t="s">
+        <v>671</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
@@ -4489,16 +4812,16 @@
         <v>381</v>
       </c>
       <c r="E4" s="15" t="s">
+        <v>672</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>674</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="H4" s="15" t="s">
         <v>675</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>676</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>677</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>159</v>
@@ -4509,25 +4832,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>676</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>677</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>678</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="E5" s="22" t="s">
         <v>679</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="F5" s="21" t="s">
         <v>680</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="G5" s="21" t="s">
+        <v>677</v>
+      </c>
+      <c r="H5" s="21" t="s">
         <v>681</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>682</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>679</v>
-      </c>
-      <c r="H5" s="21" t="s">
-        <v>683</v>
       </c>
       <c r="I5" s="21" t="s">
         <v>388</v>
@@ -4538,25 +4861,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D6" s="17" t="s">
         <v>385</v>
       </c>
       <c r="E6" s="17" t="s">
+        <v>683</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>680</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>684</v>
+      </c>
+      <c r="H6" s="23" t="s">
         <v>685</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>682</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>686</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>687</v>
       </c>
       <c r="I6" s="23" t="s">
         <v>388</v>
@@ -4567,28 +4890,28 @@
         <v>3</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C7" s="24" t="s">
+        <v>682</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>680</v>
+      </c>
+      <c r="G7" s="24" t="s">
         <v>684</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="H7" s="24" t="s">
         <v>688</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="I7" s="24" t="s">
         <v>689</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>682</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>686</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>690</v>
-      </c>
-      <c r="I7" s="24" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -4596,28 +4919,28 @@
         <v>4</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>394</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -4625,28 +4948,28 @@
         <v>5</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="F9" s="24" t="s">
         <v>694</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="G9" s="24" t="s">
         <v>695</v>
       </c>
-      <c r="F9" s="24" t="s">
-        <v>696</v>
-      </c>
-      <c r="G9" s="24" t="s">
-        <v>697</v>
-      </c>
       <c r="H9" s="24" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -4654,25 +4977,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="21" t="s">
+        <v>696</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>677</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>698</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>679</v>
-      </c>
-      <c r="D10" s="22" t="s">
+      <c r="F10" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>677</v>
+      </c>
+      <c r="H10" s="21" t="s">
         <v>699</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>700</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>682</v>
-      </c>
-      <c r="G10" s="21" t="s">
-        <v>679</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>701</v>
       </c>
       <c r="I10" s="21" t="s">
         <v>388</v>
@@ -4683,28 +5006,28 @@
         <v>7</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>392</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H11" s="24" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -4712,28 +5035,28 @@
         <v>8</v>
       </c>
       <c r="B12" s="23" t="s">
+        <v>696</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>682</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>702</v>
+      </c>
+      <c r="E12" s="17" t="s">
         <v>698</v>
       </c>
-      <c r="C12" s="23" t="s">
-        <v>684</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>704</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>700</v>
-      </c>
       <c r="F12" s="23" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -4741,28 +5064,28 @@
         <v>9</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -4770,28 +5093,28 @@
         <v>10</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D14" s="17" t="s">
         <v>405</v>
       </c>
       <c r="E14" s="17" t="s">
+        <v>705</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>706</v>
+      </c>
+      <c r="G14" s="23" t="s">
         <v>707</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="H14" s="23" t="s">
         <v>708</v>
       </c>
-      <c r="G14" s="23" t="s">
-        <v>709</v>
-      </c>
-      <c r="H14" s="23" t="s">
-        <v>710</v>
-      </c>
       <c r="I14" s="23" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -4799,25 +5122,25 @@
         <v>11</v>
       </c>
       <c r="B15" s="21" t="s">
+        <v>709</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>677</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>710</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>711</v>
       </c>
-      <c r="C15" s="21" t="s">
-        <v>679</v>
-      </c>
-      <c r="D15" s="22" t="s">
+      <c r="F15" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>677</v>
+      </c>
+      <c r="H15" s="21" t="s">
         <v>712</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>713</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>682</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>679</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>714</v>
       </c>
       <c r="I15" s="21" t="s">
         <v>388</v>
@@ -4828,28 +5151,28 @@
         <v>12</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D16" s="17" t="s">
         <v>398</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -4857,28 +5180,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>401</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H17" s="24" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -4886,28 +5209,28 @@
         <v>14</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D18" s="17" t="s">
+        <v>714</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>715</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>706</v>
+      </c>
+      <c r="G18" s="23" t="s">
         <v>716</v>
       </c>
-      <c r="E18" s="17" t="s">
-        <v>717</v>
-      </c>
-      <c r="F18" s="23" t="s">
+      <c r="H18" s="23" t="s">
         <v>708</v>
       </c>
-      <c r="G18" s="23" t="s">
-        <v>718</v>
-      </c>
-      <c r="H18" s="23" t="s">
-        <v>710</v>
-      </c>
       <c r="I18" s="23" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -4915,28 +5238,28 @@
         <v>15</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>718</v>
+      </c>
+      <c r="F19" s="24" t="s">
         <v>719</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>720</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>721</v>
-      </c>
       <c r="G19" s="24" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H19" s="24" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="32" x14ac:dyDescent="0.2">
@@ -4944,25 +5267,25 @@
         <v>16</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D20" s="17" t="s">
+        <v>720</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>721</v>
+      </c>
+      <c r="F20" s="17" t="s">
         <v>722</v>
       </c>
-      <c r="E20" s="17" t="s">
-        <v>723</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>724</v>
-      </c>
       <c r="G20" s="17" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>388</v>
@@ -4973,25 +5296,25 @@
         <v>17</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C21" s="17" t="s">
+        <v>682</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>723</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>724</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>680</v>
+      </c>
+      <c r="G21" s="17" t="s">
         <v>684</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>725</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>726</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>682</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>686</v>
-      </c>
       <c r="H21" s="17" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="I21" s="17" t="s">
         <v>388</v>
@@ -5002,67 +5325,67 @@
         <v>18</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="I22" s="17" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="30" t="s">
-        <v>729</v>
-      </c>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
+      <c r="A24" s="34" t="s">
+        <v>727</v>
+      </c>
+      <c r="B24" s="34"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
     </row>
     <row r="25" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="26">
         <v>19</v>
       </c>
       <c r="B25" s="26" t="s">
+        <v>728</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>729</v>
+      </c>
+      <c r="D25" s="26" t="s">
         <v>730</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="E25" s="26" t="s">
         <v>731</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="F25" s="26" t="s">
         <v>732</v>
       </c>
-      <c r="E25" s="26" t="s">
-        <v>733</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>734</v>
-      </c>
       <c r="G25" s="26" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H25" s="26" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="I25" s="26" t="s">
         <v>388</v>
@@ -5073,25 +5396,25 @@
         <v>20</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D26" s="26" t="s">
+        <v>733</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>734</v>
+      </c>
+      <c r="F26" s="26" t="s">
         <v>735</v>
       </c>
-      <c r="E26" s="26" t="s">
-        <v>736</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>737</v>
-      </c>
       <c r="G26" s="26" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H26" s="26" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="I26" s="26" t="s">
         <v>388</v>
@@ -5102,25 +5425,25 @@
         <v>21</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G27" s="26" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="I27" s="26" t="s">
         <v>388</v>
@@ -5131,42 +5454,42 @@
         <v>22</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="F28" s="26" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="I28" s="26" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="42" t="s">
-        <v>742</v>
-      </c>
-      <c r="B30" s="42"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="42"/>
+      <c r="A30" s="44" t="s">
+        <v>740</v>
+      </c>
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5196,11 +5519,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -5434,8 +5757,364 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4931F7-CC8F-8946-808D-95EDE4280EDF}">
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="111.1640625" customWidth="1"/>
+    <col min="2" max="2" width="118.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="20" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
+        <v>886</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="47" t="s">
+        <v>887</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>888</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+    </row>
+    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="47" t="s">
+        <v>889</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>890</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+    </row>
+    <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="47" t="s">
+        <v>891</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>892</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+    </row>
+    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="47" t="s">
+        <v>893</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>894</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="47" t="s">
+        <v>895</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>896</v>
+      </c>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+    </row>
+    <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="47" t="s">
+        <v>897</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>898</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+    </row>
+    <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="47" t="s">
+        <v>899</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>900</v>
+      </c>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="47" t="s">
+        <v>901</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>902</v>
+      </c>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+    </row>
+    <row r="12" spans="1:9" ht="20" x14ac:dyDescent="0.25">
+      <c r="A12" s="46" t="s">
+        <v>903</v>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+    </row>
+    <row r="14" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="47" t="s">
+        <v>904</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+    </row>
+    <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="47" t="s">
+        <v>905</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+    </row>
+    <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="47" t="s">
+        <v>906</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+    </row>
+    <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="47" t="s">
+        <v>907</v>
+      </c>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+    </row>
+    <row r="18" spans="1:9" ht="32" x14ac:dyDescent="0.2">
+      <c r="A18" s="47" t="s">
+        <v>908</v>
+      </c>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+    </row>
+    <row r="20" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="A20" s="47" t="s">
+        <v>909</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+    </row>
+    <row r="22" spans="1:9" ht="20" x14ac:dyDescent="0.25">
+      <c r="A22" s="46" t="s">
+        <v>910</v>
+      </c>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+    </row>
+    <row r="24" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="A24" s="47" t="s">
+        <v>911</v>
+      </c>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+    </row>
+    <row r="25" spans="1:9" ht="64" x14ac:dyDescent="0.2">
+      <c r="A25" s="47" t="s">
+        <v>912</v>
+      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+    </row>
+    <row r="26" spans="1:9" ht="48" x14ac:dyDescent="0.2">
+      <c r="A26" s="47" t="s">
+        <v>913</v>
+      </c>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C59208D-E153-D94F-949B-1D2F26D7FF23}">
-  <dimension ref="A1:J202"/>
+  <dimension ref="A1:J208"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="58" customWidth="1"/>
@@ -5466,7 +6145,7 @@
         <v>553</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -5499,7 +6178,7 @@
         <v>554</v>
       </c>
       <c r="G3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -5528,7 +6207,7 @@
         <v>554</v>
       </c>
       <c r="G5" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -5546,7 +6225,7 @@
         <v>554</v>
       </c>
       <c r="G6" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -5563,7 +6242,7 @@
         <v>554</v>
       </c>
       <c r="G7" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -5580,7 +6259,7 @@
         <v>554</v>
       </c>
       <c r="G8" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="H8" t="s">
         <v>476</v>
@@ -5601,7 +6280,7 @@
         <v>554</v>
       </c>
       <c r="G9" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
@@ -5631,7 +6310,7 @@
         <v>554</v>
       </c>
       <c r="G11" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -5649,7 +6328,7 @@
         <v>554</v>
       </c>
       <c r="G12" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -5667,7 +6346,7 @@
         <v>554</v>
       </c>
       <c r="G13" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -5685,7 +6364,7 @@
         <v>554</v>
       </c>
       <c r="G14" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -5718,7 +6397,7 @@
         <v>554</v>
       </c>
       <c r="G16" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -5736,7 +6415,7 @@
         <v>554</v>
       </c>
       <c r="G17" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -5754,7 +6433,7 @@
         <v>554</v>
       </c>
       <c r="G18" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="J18" t="s">
         <v>476</v>
@@ -5775,7 +6454,7 @@
         <v>554</v>
       </c>
       <c r="G19" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -5793,7 +6472,7 @@
         <v>554</v>
       </c>
       <c r="G20" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="I20" t="s">
         <v>476</v>
@@ -5814,7 +6493,7 @@
         <v>554</v>
       </c>
       <c r="G21" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
@@ -5847,7 +6526,7 @@
         <v>554</v>
       </c>
       <c r="G23" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -5865,7 +6544,7 @@
         <v>554</v>
       </c>
       <c r="G24" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -5883,7 +6562,7 @@
         <v>554</v>
       </c>
       <c r="G25" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -5913,7 +6592,7 @@
         <v>554</v>
       </c>
       <c r="G27" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -5930,6 +6609,9 @@
       <c r="E28" t="s">
         <v>555</v>
       </c>
+      <c r="G28" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -5945,6 +6627,9 @@
       <c r="E29" t="s">
         <v>555</v>
       </c>
+      <c r="G29" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
@@ -5960,6 +6645,9 @@
       <c r="E30" t="s">
         <v>555</v>
       </c>
+      <c r="G30" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
@@ -5975,6 +6663,9 @@
       <c r="E31" t="s">
         <v>555</v>
       </c>
+      <c r="G31" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
@@ -5990,6 +6681,9 @@
       <c r="E32" t="s">
         <v>555</v>
       </c>
+      <c r="G32" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
@@ -6005,6 +6699,9 @@
       <c r="E33" t="s">
         <v>555</v>
       </c>
+      <c r="G33" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
@@ -6020,6 +6717,9 @@
       <c r="E34" t="s">
         <v>555</v>
       </c>
+      <c r="G34" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
@@ -6033,7 +6733,7 @@
         <v>431</v>
       </c>
       <c r="G35" t="s">
-        <v>476</v>
+        <v>865</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
@@ -6050,6 +6750,9 @@
       <c r="E36" t="s">
         <v>555</v>
       </c>
+      <c r="G36" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
@@ -6065,6 +6768,9 @@
       <c r="E37" t="s">
         <v>555</v>
       </c>
+      <c r="G37" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
@@ -6080,6 +6786,9 @@
       <c r="E38" t="s">
         <v>555</v>
       </c>
+      <c r="G38" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
@@ -6095,6 +6804,9 @@
       <c r="E39" t="s">
         <v>555</v>
       </c>
+      <c r="G39" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
@@ -6110,6 +6822,9 @@
       <c r="E40" t="s">
         <v>555</v>
       </c>
+      <c r="G40" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
@@ -6125,6 +6840,9 @@
       <c r="E41" t="s">
         <v>555</v>
       </c>
+      <c r="G41" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
@@ -6139,6 +6857,9 @@
       <c r="E42" t="s">
         <v>555</v>
       </c>
+      <c r="G42" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
@@ -6154,6 +6875,9 @@
       <c r="E43" t="s">
         <v>555</v>
       </c>
+      <c r="G43" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
@@ -6166,6 +6890,9 @@
       <c r="D44" t="s">
         <v>461</v>
       </c>
+      <c r="G44" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
@@ -6181,6 +6908,9 @@
       <c r="E45" t="s">
         <v>555</v>
       </c>
+      <c r="G45" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
@@ -6196,6 +6926,9 @@
       <c r="E46" t="s">
         <v>555</v>
       </c>
+      <c r="G46" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
@@ -6211,6 +6944,9 @@
       <c r="E47" t="s">
         <v>555</v>
       </c>
+      <c r="G47" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
@@ -6229,6 +6965,9 @@
       <c r="F48" t="s">
         <v>476</v>
       </c>
+      <c r="G48" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
@@ -6244,6 +6983,9 @@
       <c r="E49" t="s">
         <v>555</v>
       </c>
+      <c r="G49" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
@@ -6259,6 +7001,9 @@
       <c r="E50" t="s">
         <v>555</v>
       </c>
+      <c r="G50" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
@@ -6274,6 +7019,9 @@
       <c r="E51" t="s">
         <v>555</v>
       </c>
+      <c r="G51" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
@@ -6289,6 +7037,9 @@
       <c r="E52" t="s">
         <v>555</v>
       </c>
+      <c r="G52" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
@@ -6304,6 +7055,9 @@
       <c r="E53" t="s">
         <v>555</v>
       </c>
+      <c r="G53" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
@@ -6319,6 +7073,9 @@
       <c r="E54" t="s">
         <v>555</v>
       </c>
+      <c r="G54" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
@@ -6334,6 +7091,9 @@
       <c r="E55" t="s">
         <v>555</v>
       </c>
+      <c r="G55" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
@@ -6349,6 +7109,9 @@
       <c r="E56" t="s">
         <v>555</v>
       </c>
+      <c r="G56" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
@@ -6364,6 +7127,9 @@
       <c r="E57" t="s">
         <v>555</v>
       </c>
+      <c r="G57" t="s">
+        <v>865</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
@@ -6392,6 +7158,9 @@
       <c r="E59" t="s">
         <v>555</v>
       </c>
+      <c r="G59" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
@@ -6406,6 +7175,9 @@
       <c r="E60" t="s">
         <v>555</v>
       </c>
+      <c r="G60" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
@@ -6420,6 +7192,9 @@
       <c r="E61" t="s">
         <v>555</v>
       </c>
+      <c r="G61" t="s">
+        <v>917</v>
+      </c>
       <c r="H61" t="s">
         <v>476</v>
       </c>
@@ -6451,6 +7226,9 @@
       <c r="E63" t="s">
         <v>555</v>
       </c>
+      <c r="G63" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
@@ -6465,8 +7243,11 @@
       <c r="E64" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G64" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>516</v>
       </c>
@@ -6479,355 +7260,376 @@
       <c r="E65" t="s">
         <v>555</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G65" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="B66" t="s">
         <v>416</v>
       </c>
       <c r="D66" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="E66" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+      <c r="G66" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B67" t="s">
         <v>416</v>
       </c>
       <c r="D67" t="s">
+        <v>795</v>
+      </c>
+      <c r="E67" t="s">
+        <v>847</v>
+      </c>
+      <c r="G67" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
         <v>797</v>
-      </c>
-      <c r="E67" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>799</v>
       </c>
       <c r="B68" t="s">
         <v>416</v>
       </c>
       <c r="D68" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="E68" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+      <c r="G68" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B69" t="s">
         <v>416</v>
       </c>
       <c r="D69" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E69" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+      <c r="G69" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B70" t="s">
         <v>416</v>
       </c>
       <c r="D70" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E70" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+      <c r="G70" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B71" t="s">
         <v>416</v>
       </c>
       <c r="D71" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E71" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>807</v>
+        <v>847</v>
+      </c>
+      <c r="G71" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="48" t="s">
+        <v>805</v>
       </c>
       <c r="B72" t="s">
         <v>416</v>
       </c>
       <c r="D72" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E72" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B73" t="s">
         <v>416</v>
       </c>
       <c r="D73" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E73" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="B74" t="s">
         <v>416</v>
       </c>
       <c r="D74" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E74" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B75" t="s">
         <v>416</v>
       </c>
       <c r="D75" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="E75" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="B76" t="s">
         <v>416</v>
       </c>
       <c r="D76" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E76" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="B77" t="s">
         <v>416</v>
       </c>
       <c r="D77" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="E77" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B78" t="s">
         <v>416</v>
       </c>
       <c r="D78" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E78" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B79" t="s">
         <v>416</v>
       </c>
       <c r="D79" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E79" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B80" t="s">
         <v>416</v>
       </c>
       <c r="D80" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="E80" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="B81" t="s">
         <v>416</v>
       </c>
       <c r="D81" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E81" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B82" t="s">
         <v>416</v>
       </c>
       <c r="D82" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E82" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B83" t="s">
         <v>416</v>
       </c>
       <c r="D83" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E83" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B84" t="s">
         <v>416</v>
       </c>
       <c r="D84" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E84" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="B85" t="s">
         <v>416</v>
       </c>
       <c r="D85" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E85" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="B86" t="s">
         <v>416</v>
       </c>
       <c r="D86" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E86" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B87" t="s">
         <v>416</v>
       </c>
       <c r="D87" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E87" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B88" t="s">
         <v>416</v>
       </c>
       <c r="D88" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E88" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="B89" t="s">
         <v>416</v>
       </c>
       <c r="D89" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E89" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="B90" t="s">
         <v>416</v>
       </c>
       <c r="D90" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E90" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.2">
@@ -6841,1094 +7643,1337 @@
         <v>598</v>
       </c>
       <c r="E91" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B92" t="s">
         <v>416</v>
       </c>
       <c r="D92" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E92" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B93" t="s">
         <v>416</v>
       </c>
       <c r="D93" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E93" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="C102" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" s="45" t="s">
+        <v>866</v>
+      </c>
+      <c r="B94" t="s">
+        <v>166</v>
+      </c>
+      <c r="D94" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>868</v>
+      </c>
+      <c r="B95" t="s">
+        <v>166</v>
+      </c>
+      <c r="D95" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>870</v>
+      </c>
+      <c r="B96" t="s">
+        <v>419</v>
+      </c>
+      <c r="D96" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>872</v>
+      </c>
+      <c r="B97" t="s">
+        <v>416</v>
+      </c>
+      <c r="D97" t="s">
+        <v>873</v>
+      </c>
+      <c r="F97" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>875</v>
+      </c>
+      <c r="B98" t="s">
+        <v>419</v>
+      </c>
+      <c r="D98" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>877</v>
+      </c>
+      <c r="B99" t="s">
+        <v>166</v>
+      </c>
+      <c r="D99" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" s="45" t="s">
+        <v>878</v>
+      </c>
+      <c r="B100" t="s">
+        <v>416</v>
+      </c>
+      <c r="D100" t="s">
+        <v>879</v>
+      </c>
+      <c r="F100" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>880</v>
+      </c>
+      <c r="B101" t="s">
+        <v>416</v>
+      </c>
+      <c r="D101" t="s">
+        <v>881</v>
+      </c>
+      <c r="F101" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>882</v>
+      </c>
+      <c r="B102" t="s">
+        <v>416</v>
+      </c>
+      <c r="D102" t="s">
+        <v>883</v>
+      </c>
+      <c r="F102" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>884</v>
+      </c>
+      <c r="B103" t="s">
+        <v>166</v>
+      </c>
+      <c r="D103" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B105" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="C111" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B112" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="C112" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D112" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="E112" s="20" t="s">
+        <v>551</v>
+      </c>
+      <c r="F112" s="20" t="s">
+        <v>553</v>
+      </c>
+      <c r="G112" s="20" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
         <v>342</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B113" t="s">
         <v>419</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D113" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
         <v>340</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B114" t="s">
         <v>419</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D114" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
+    <row r="115" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
         <v>337</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B115" t="s">
         <v>419</v>
       </c>
-      <c r="D106" s="18" t="s">
+      <c r="D115" s="18" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
         <v>344</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B116" t="s">
         <v>419</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D116" t="s">
         <v>426</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H116" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
         <v>345</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B118" t="s">
         <v>166</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D118" t="s">
         <v>435</v>
-      </c>
-      <c r="E109" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>335</v>
-      </c>
-      <c r="B110" t="s">
-        <v>166</v>
-      </c>
-      <c r="D110" t="s">
-        <v>414</v>
-      </c>
-      <c r="E110" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>338</v>
-      </c>
-      <c r="B111" t="s">
-        <v>166</v>
-      </c>
-      <c r="D111" t="s">
-        <v>420</v>
-      </c>
-      <c r="E111" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>313</v>
-      </c>
-      <c r="B112" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C112" s="19"/>
-      <c r="D112" t="s">
-        <v>492</v>
-      </c>
-      <c r="E112" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
-        <v>446</v>
-      </c>
-      <c r="B113" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C113" s="19"/>
-      <c r="D113" t="s">
-        <v>445</v>
-      </c>
-      <c r="E113" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>346</v>
-      </c>
-      <c r="B114" t="s">
-        <v>166</v>
-      </c>
-      <c r="D114" t="s">
-        <v>436</v>
-      </c>
-      <c r="E114" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>311</v>
-      </c>
-      <c r="B115" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C115" s="19"/>
-      <c r="D115" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
-        <v>322</v>
-      </c>
-      <c r="B116" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C116" s="19"/>
-      <c r="D116" t="s">
-        <v>488</v>
-      </c>
-      <c r="E116" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>327</v>
-      </c>
-      <c r="B117" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C117" s="19"/>
-      <c r="D117" t="s">
-        <v>487</v>
-      </c>
-      <c r="E117" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>309</v>
-      </c>
-      <c r="B118" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C118" s="19"/>
-      <c r="D118" t="s">
-        <v>498</v>
       </c>
       <c r="E118" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>310</v>
-      </c>
-      <c r="B119" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="B119" t="s">
         <v>166</v>
       </c>
-      <c r="C119" s="19"/>
       <c r="D119" t="s">
-        <v>500</v>
+        <v>414</v>
       </c>
       <c r="E119" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>509</v>
+        <v>338</v>
       </c>
       <c r="B120" t="s">
         <v>166</v>
       </c>
       <c r="D120" t="s">
-        <v>510</v>
+        <v>420</v>
       </c>
       <c r="E120" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B121" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C121" s="19"/>
       <c r="D121" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E121" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>558</v>
+        <v>446</v>
       </c>
       <c r="B122" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C122" t="s">
-        <v>557</v>
-      </c>
+      <c r="C122" s="19"/>
       <c r="D122" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.2">
+        <v>445</v>
+      </c>
+      <c r="E122" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>560</v>
-      </c>
-      <c r="B123" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="B123" t="s">
         <v>166</v>
       </c>
-      <c r="C123" t="s">
-        <v>557</v>
-      </c>
       <c r="D123" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+      <c r="E123" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>562</v>
+        <v>311</v>
       </c>
       <c r="B124" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C124" t="s">
-        <v>557</v>
-      </c>
+      <c r="C124" s="19"/>
       <c r="D124" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>565</v>
+        <v>322</v>
       </c>
       <c r="B125" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C125" t="s">
-        <v>564</v>
-      </c>
+      <c r="C125" s="19"/>
       <c r="D125" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+      <c r="E125" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>567</v>
+        <v>327</v>
       </c>
       <c r="B126" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C126" t="s">
-        <v>564</v>
-      </c>
+      <c r="C126" s="19"/>
       <c r="D126" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.2">
+        <v>487</v>
+      </c>
+      <c r="E126" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>569</v>
+        <v>309</v>
       </c>
       <c r="B127" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C127" t="s">
-        <v>570</v>
-      </c>
+      <c r="C127" s="19"/>
       <c r="D127" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.2">
+        <v>498</v>
+      </c>
+      <c r="E127" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>573</v>
+        <v>310</v>
       </c>
       <c r="B128" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C128" t="s">
-        <v>572</v>
-      </c>
+      <c r="C128" s="19"/>
       <c r="D128" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+        <v>500</v>
+      </c>
+      <c r="E128" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>574</v>
-      </c>
-      <c r="B129" s="19" t="s">
+        <v>509</v>
+      </c>
+      <c r="B129" t="s">
         <v>166</v>
       </c>
-      <c r="C129" t="s">
-        <v>572</v>
-      </c>
       <c r="D129" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+        <v>510</v>
+      </c>
+      <c r="E129" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>578</v>
+        <v>315</v>
       </c>
       <c r="B130" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C130" t="s">
-        <v>572</v>
-      </c>
+      <c r="C130" s="19"/>
       <c r="D130" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+        <v>497</v>
+      </c>
+      <c r="E130" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="B131" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C131" t="s">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="D131" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+        <v>559</v>
+      </c>
+      <c r="F131" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="B132" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C132" t="s">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="D132" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+        <v>561</v>
+      </c>
+      <c r="F132" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>585</v>
+        <v>562</v>
       </c>
       <c r="B133" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C133" t="s">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="D133" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+        <v>563</v>
+      </c>
+      <c r="F133" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>587</v>
+        <v>565</v>
       </c>
       <c r="B134" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C134" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="D134" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+        <v>566</v>
+      </c>
+      <c r="F134" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>590</v>
+        <v>567</v>
       </c>
       <c r="B135" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C135" t="s">
-        <v>589</v>
+        <v>564</v>
       </c>
       <c r="D135" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+        <v>568</v>
+      </c>
+      <c r="F135" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>593</v>
+        <v>569</v>
       </c>
       <c r="B136" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C136" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="D136" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+        <v>571</v>
+      </c>
+      <c r="F136" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>595</v>
+        <v>573</v>
       </c>
       <c r="B137" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C137" t="s">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="D137" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+        <v>576</v>
+      </c>
+      <c r="F137" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>597</v>
+        <v>574</v>
       </c>
       <c r="B138" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C138" t="s">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="D138" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+        <v>577</v>
+      </c>
+      <c r="F138" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="B139" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C139" t="s">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="D139" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+        <v>575</v>
+      </c>
+      <c r="F139" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>602</v>
+        <v>580</v>
       </c>
       <c r="B140" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C140" t="s">
-        <v>601</v>
+        <v>579</v>
       </c>
       <c r="D140" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+        <v>581</v>
+      </c>
+      <c r="F140" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>605</v>
+        <v>583</v>
       </c>
       <c r="B141" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C141" t="s">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="D141" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+        <v>584</v>
+      </c>
+      <c r="F141" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="B142" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C142" t="s">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="D142" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+        <v>586</v>
+      </c>
+      <c r="F142" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>610</v>
+        <v>587</v>
       </c>
       <c r="B143" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C143" t="s">
-        <v>609</v>
+        <v>582</v>
       </c>
       <c r="D143" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+        <v>588</v>
+      </c>
+      <c r="F143" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>335</v>
+        <v>590</v>
       </c>
       <c r="B144" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C144" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="D144" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+        <v>591</v>
+      </c>
+      <c r="F144" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>613</v>
+        <v>593</v>
       </c>
       <c r="B145" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C145" t="s">
-        <v>612</v>
+        <v>589</v>
       </c>
       <c r="D145" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+        <v>592</v>
+      </c>
+      <c r="F145" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="B146" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C146" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="D146" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+        <v>596</v>
+      </c>
+      <c r="F146" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>617</v>
+        <v>599</v>
       </c>
       <c r="B147" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C147" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="D147" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+      <c r="F147" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>619</v>
+        <v>602</v>
       </c>
       <c r="B148" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C148" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="D148" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+        <v>603</v>
+      </c>
+      <c r="F148" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="B149" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C149" t="s">
-        <v>623</v>
+        <v>604</v>
       </c>
       <c r="D149" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+        <v>606</v>
+      </c>
+      <c r="F149" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>625</v>
+        <v>607</v>
       </c>
       <c r="B150" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C150" t="s">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="D150" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+        <v>608</v>
+      </c>
+      <c r="F150" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>627</v>
+        <v>610</v>
       </c>
       <c r="B151" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C151" t="s">
-        <v>624</v>
+        <v>609</v>
       </c>
       <c r="D151" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+        <v>611</v>
+      </c>
+      <c r="F151" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="B152" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C152" t="s">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="D152" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+        <v>614</v>
+      </c>
+      <c r="F152" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="B153" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C153" t="s">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="D153" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+        <v>616</v>
+      </c>
+      <c r="F153" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>635</v>
+        <v>617</v>
       </c>
       <c r="B154" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C154" t="s">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="D154" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+        <v>618</v>
+      </c>
+      <c r="F154" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>637</v>
+        <v>619</v>
       </c>
       <c r="B155" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C155" t="s">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="D155" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+        <v>620</v>
+      </c>
+      <c r="F155" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>639</v>
+        <v>621</v>
       </c>
       <c r="B156" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C156" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="D156" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+        <v>622</v>
+      </c>
+      <c r="F156" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>641</v>
+        <v>625</v>
       </c>
       <c r="B157" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C157" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="D157" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+        <v>626</v>
+      </c>
+      <c r="F157" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
       <c r="B158" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C158" t="s">
-        <v>644</v>
+        <v>624</v>
       </c>
       <c r="D158" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+        <v>628</v>
+      </c>
+      <c r="F158" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="B159" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C159" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="D159" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+        <v>631</v>
+      </c>
+      <c r="F159" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>648</v>
+        <v>632</v>
       </c>
       <c r="B160" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C160" t="s">
-        <v>644</v>
+        <v>629</v>
       </c>
       <c r="D160" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+        <v>633</v>
+      </c>
+      <c r="F160" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>651</v>
+        <v>635</v>
       </c>
       <c r="B161" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C161" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="D161" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+        <v>636</v>
+      </c>
+      <c r="F161" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>653</v>
+        <v>637</v>
       </c>
       <c r="B162" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C162" t="s">
-        <v>650</v>
+        <v>634</v>
       </c>
       <c r="D162" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+        <v>638</v>
+      </c>
+      <c r="F162" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="B163" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C163" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="D163" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+        <v>640</v>
+      </c>
+      <c r="F163" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="B164" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C164" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="D164" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+        <v>642</v>
+      </c>
+      <c r="F164" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="B165" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C165" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="D165" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+        <v>645</v>
+      </c>
+      <c r="F165" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
       <c r="B166" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C166" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="D166" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+        <v>647</v>
+      </c>
+      <c r="F166" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
       <c r="B167" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C167" t="s">
-        <v>660</v>
+        <v>644</v>
       </c>
       <c r="D167" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+        <v>649</v>
+      </c>
+      <c r="F167" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="B168" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C168" t="s">
-        <v>669</v>
+        <v>650</v>
       </c>
       <c r="D168" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+        <v>652</v>
+      </c>
+      <c r="F168" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>671</v>
+        <v>653</v>
       </c>
       <c r="B169" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C169" t="s">
+        <v>650</v>
+      </c>
+      <c r="D169" t="s">
+        <v>654</v>
+      </c>
+      <c r="F169" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" t="s">
+        <v>656</v>
+      </c>
+      <c r="B170" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C170" t="s">
+        <v>655</v>
+      </c>
+      <c r="D170" t="s">
+        <v>657</v>
+      </c>
+      <c r="F170" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" t="s">
+        <v>658</v>
+      </c>
+      <c r="B171" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C171" t="s">
+        <v>655</v>
+      </c>
+      <c r="D171" t="s">
+        <v>659</v>
+      </c>
+      <c r="F171" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" t="s">
+        <v>661</v>
+      </c>
+      <c r="B172" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C172" t="s">
+        <v>660</v>
+      </c>
+      <c r="D172" t="s">
+        <v>662</v>
+      </c>
+      <c r="F172" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" t="s">
+        <v>663</v>
+      </c>
+      <c r="B173" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C173" t="s">
+        <v>660</v>
+      </c>
+      <c r="D173" t="s">
+        <v>664</v>
+      </c>
+      <c r="F173" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" t="s">
+        <v>665</v>
+      </c>
+      <c r="B174" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C174" t="s">
+        <v>667</v>
+      </c>
+      <c r="D174" t="s">
+        <v>666</v>
+      </c>
+      <c r="F174" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" t="s">
         <v>669</v>
       </c>
-      <c r="D169" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B170" s="19"/>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="D174" t="s">
+      <c r="B175" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C175" t="s">
+        <v>667</v>
+      </c>
+      <c r="D175" t="s">
+        <v>668</v>
+      </c>
+      <c r="F175" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B176" s="19"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D180" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A176" t="s">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A182" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A177" t="s">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A183" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A178" t="s">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A184" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A179" t="s">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A185" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A180" t="s">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A186" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A181" t="s">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A187" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A188" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A183" t="s">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A189" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A184" t="s">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A190" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A185" t="s">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A191" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A186" t="s">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A192" t="s">
         <v>525</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A187" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A188" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A189" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A190" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A191" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A192" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="193" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
     </row>
     <row r="196" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="197" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="198" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="199" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="200" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
     </row>
     <row r="201" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
     </row>
     <row r="202" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A203" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A204" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A205" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A206" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A207" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A208" t="s">
         <v>550</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D119">
-    <sortCondition descending="1" ref="B2:B119"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D128">
+    <sortCondition descending="1" ref="B2:B128"/>
   </sortState>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7951,30 +8996,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -8006,17 +9051,17 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
     </row>
     <row r="6" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
@@ -8154,17 +9199,17 @@
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
     </row>
     <row r="12" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
@@ -8302,17 +9347,17 @@
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
@@ -8450,17 +9495,17 @@
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
     </row>
     <row r="24" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
@@ -8598,17 +9643,17 @@
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
     </row>
     <row r="30" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
@@ -8746,17 +9791,17 @@
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
     </row>
     <row r="36" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
@@ -8927,40 +9972,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="32"/>
-      <c r="N3" s="32"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
     </row>
     <row r="4" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -10989,16 +12034,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="31"/>
+      <c r="B1" s="35"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="30"/>
+      <c r="B4" s="34"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
@@ -11017,10 +12062,10 @@
       </c>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="30"/>
+      <c r="B8" s="34"/>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
@@ -11039,10 +12084,10 @@
       </c>
     </row>
     <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="B12" s="30"/>
+      <c r="B12" s="34"/>
     </row>
     <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
@@ -11061,10 +12106,10 @@
       </c>
     </row>
     <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="B16" s="30"/>
+      <c r="B16" s="34"/>
     </row>
     <row r="17" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7" t="s">
@@ -11083,10 +12128,10 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="34" t="s">
         <v>194</v>
       </c>
-      <c r="B20" s="30"/>
+      <c r="B20" s="34"/>
     </row>
     <row r="21" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
@@ -11097,18 +12142,18 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="35" t="s">
+      <c r="A24" s="37" t="s">
         <v>351</v>
       </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="38" t="s">
         <v>352</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B27" s="14" t="s">
@@ -11119,11 +12164,11 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="34" t="s">
         <v>355</v>
       </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="34"/>
     </row>
     <row r="29" spans="1:3" ht="48" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
@@ -11148,11 +12193,11 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="34" t="s">
         <v>360</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="34"/>
     </row>
     <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="7" t="s">
@@ -11177,11 +12222,11 @@
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="34" t="s">
         <v>365</v>
       </c>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
     </row>
     <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
@@ -11206,11 +12251,11 @@
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="30" t="s">
+      <c r="A40" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
     </row>
     <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="s">
@@ -11235,11 +12280,11 @@
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="30" t="s">
+      <c r="A44" s="34" t="s">
         <v>374</v>
       </c>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
     </row>
     <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="7" t="s">
@@ -11265,12 +12310,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A24:C24"/>
@@ -11278,6 +12317,12 @@
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -11297,13 +12342,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -11618,24 +12663,24 @@
       <c r="E45" s="6"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="37" t="s">
+      <c r="A47" s="39" t="s">
         <v>205</v>
       </c>
-      <c r="B47" s="37"/>
-      <c r="D47" s="37" t="s">
+      <c r="B47" s="39"/>
+      <c r="D47" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="E47" s="37"/>
+      <c r="E47" s="39"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="38" t="s">
+      <c r="A48" s="40" t="s">
         <v>207</v>
       </c>
-      <c r="B48" s="38"/>
-      <c r="D48" s="38" t="s">
+      <c r="B48" s="40"/>
+      <c r="D48" s="40" t="s">
         <v>208</v>
       </c>
-      <c r="E48" s="38"/>
+      <c r="E48" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -11660,17 +12705,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -12002,17 +13047,17 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="39" t="s">
+      <c r="A15" s="41" t="s">
         <v>229</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="39"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12037,15 +13082,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -12253,24 +13298,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="42" t="s">
         <v>378</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="33" t="s">
         <v>379</v>
       </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
@@ -12518,18 +13563,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="43" t="s">
         <v>281</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -12579,83 +13624,83 @@
       <c r="C8" s="6"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="43" t="s">
-        <v>865</v>
+      <c r="A10" s="30" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="31" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.25">
+      <c r="A14" s="31" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="31" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" s="30" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="44" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" s="31" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="43" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="31" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="44" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="31" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="44" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="30" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="44" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="31" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="43" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" s="31" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="44" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" s="31" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" s="44" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" s="30" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" s="44" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" s="30" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="43" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" s="30" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="43" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" s="30" t="s">
         <v>862</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="43" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="43" t="s">
-        <v>864</v>
       </c>
     </row>
   </sheetData>
